--- a/ISO 90012026 Readiness Checker - Sample.xlsx
+++ b/ISO 90012026 Readiness Checker - Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A350CC5D-FFB7-4FF4-93E4-44A000E373BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD92497-6C39-45F5-B9C6-E40FAB839EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="917" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="917" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Audit Summary" sheetId="30" r:id="rId1"/>
@@ -463,28 +463,6 @@
     </comment>
   </commentList>
 </comments>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3243,7 +3221,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="31" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3297,6 +3274,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6773,8 +6753,8 @@
         <v>188</v>
       </c>
       <c r="E34" s="289"/>
-      <c r="F34" s="235" t="str" cm="1">
-        <f t="array" ref="F34:F35">'Audit Scoring Detail'!E10:E11</f>
+      <c r="F34" s="235" t="str">
+        <f>'Audit Scoring Detail'!E10</f>
         <v>Failed</v>
       </c>
       <c r="G34" s="221"/>
@@ -6784,8 +6764,8 @@
         <v>188</v>
       </c>
       <c r="K34" s="289"/>
-      <c r="L34" s="235" t="str" cm="1">
-        <f t="array" ref="L34:L35">'Audit Scoring Detail'!E17:E18</f>
+      <c r="L34" s="235" t="str">
+        <f>'Audit Scoring Detail'!E17</f>
         <v>Optimal</v>
       </c>
       <c r="M34" s="321"/>
@@ -6807,17 +6787,13 @@
       <c r="C35" s="236"/>
       <c r="D35" s="237"/>
       <c r="E35" s="237"/>
-      <c r="F35" s="237">
-        <v>0</v>
-      </c>
+      <c r="F35" s="237"/>
       <c r="G35" s="185"/>
       <c r="H35" s="223"/>
       <c r="I35" s="238"/>
       <c r="J35" s="237"/>
       <c r="K35" s="237"/>
-      <c r="L35" s="237">
-        <v>0</v>
-      </c>
+      <c r="L35" s="280"/>
       <c r="M35" s="322"/>
       <c r="N35" s="194"/>
       <c r="O35" s="305"/>
@@ -9814,7 +9790,7 @@
       <c r="S58" s="1"/>
     </row>
     <row r="59" spans="2:36" ht="15" customHeight="1">
-      <c r="D59" s="280"/>
+      <c r="D59" s="279"/>
       <c r="F59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -10738,8 +10714,8 @@
     </row>
     <row r="8" spans="2:12" ht="150" customHeight="1">
       <c r="B8" s="35"/>
-      <c r="C8" s="264"/>
-      <c r="D8" s="265" t="s">
+      <c r="C8" s="53"/>
+      <c r="D8" s="264" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="90" t="s">
@@ -10762,8 +10738,8 @@
     </row>
     <row r="9" spans="2:12" ht="150" customHeight="1">
       <c r="B9" s="35"/>
-      <c r="C9" s="264"/>
-      <c r="D9" s="266" t="s">
+      <c r="C9" s="53"/>
+      <c r="D9" s="265" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="92" t="s">
@@ -10786,8 +10762,8 @@
     </row>
     <row r="10" spans="2:12" ht="150" customHeight="1">
       <c r="B10" s="35"/>
-      <c r="C10" s="264"/>
-      <c r="D10" s="266" t="s">
+      <c r="C10" s="53"/>
+      <c r="D10" s="265" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="94" t="s">
@@ -10810,8 +10786,8 @@
     </row>
     <row r="11" spans="2:12" ht="150" customHeight="1" thickBot="1">
       <c r="B11" s="35"/>
-      <c r="C11" s="264"/>
-      <c r="D11" s="267" t="s">
+      <c r="C11" s="53"/>
+      <c r="D11" s="266" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="96" t="s">
@@ -10834,9 +10810,7 @@
     </row>
     <row r="12" spans="2:12" s="22" customFormat="1" ht="6" customHeight="1" thickBot="1">
       <c r="B12" s="49"/>
-      <c r="C12" s="521">
-        <v>1</v>
-      </c>
+      <c r="C12" s="521"/>
       <c r="D12" s="522"/>
       <c r="E12" s="522"/>
       <c r="F12" s="522"/>
@@ -10933,7 +10907,7 @@
     <row r="18" spans="2:12" ht="150" customHeight="1">
       <c r="B18" s="35"/>
       <c r="C18" s="520"/>
-      <c r="D18" s="268" t="s">
+      <c r="D18" s="267" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="98" t="s">
@@ -10957,7 +10931,7 @@
     <row r="19" spans="2:12" ht="150" customHeight="1">
       <c r="B19" s="35"/>
       <c r="C19" s="520"/>
-      <c r="D19" s="269" t="s">
+      <c r="D19" s="268" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="92" t="s">
@@ -10997,7 +10971,7 @@
     <row r="20" spans="2:12" ht="150" customHeight="1">
       <c r="B20" s="35"/>
       <c r="C20" s="520"/>
-      <c r="D20" s="270" t="s">
+      <c r="D20" s="269" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="102" t="s">
@@ -11021,7 +10995,7 @@
     <row r="21" spans="2:12" ht="150" customHeight="1">
       <c r="B21" s="35"/>
       <c r="C21" s="520"/>
-      <c r="D21" s="269" t="s">
+      <c r="D21" s="268" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="110" t="s">
@@ -11045,7 +11019,7 @@
     <row r="22" spans="2:12" ht="150" customHeight="1" thickBot="1">
       <c r="B22" s="35"/>
       <c r="C22" s="520"/>
-      <c r="D22" s="271" t="s">
+      <c r="D22" s="270" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="104" t="s">
@@ -11181,7 +11155,7 @@
     <row r="29" spans="2:12" ht="150" customHeight="1">
       <c r="B29" s="35"/>
       <c r="C29" s="530"/>
-      <c r="D29" s="268" t="s">
+      <c r="D29" s="267" t="s">
         <v>31</v>
       </c>
       <c r="E29" s="111" t="s">
@@ -11223,7 +11197,7 @@
     <row r="30" spans="2:12" ht="150" customHeight="1">
       <c r="B30" s="35"/>
       <c r="C30" s="530"/>
-      <c r="D30" s="269" t="s">
+      <c r="D30" s="268" t="s">
         <v>32</v>
       </c>
       <c r="E30" s="107" t="s">
@@ -11263,7 +11237,7 @@
     <row r="31" spans="2:12" ht="150" customHeight="1">
       <c r="B31" s="35"/>
       <c r="C31" s="530"/>
-      <c r="D31" s="269" t="s">
+      <c r="D31" s="268" t="s">
         <v>33</v>
       </c>
       <c r="E31" s="107" t="s">
@@ -11303,7 +11277,7 @@
     <row r="32" spans="2:12" ht="150" customHeight="1" thickBot="1">
       <c r="B32" s="35"/>
       <c r="C32" s="530"/>
-      <c r="D32" s="271" t="s">
+      <c r="D32" s="270" t="s">
         <v>34</v>
       </c>
       <c r="E32" s="109" t="s">
@@ -11439,7 +11413,7 @@
     <row r="39" spans="1:19" ht="150" customHeight="1">
       <c r="B39" s="35"/>
       <c r="C39" s="520"/>
-      <c r="D39" s="265" t="s">
+      <c r="D39" s="264" t="s">
         <v>37</v>
       </c>
       <c r="E39" s="111" t="s">
@@ -11484,7 +11458,7 @@
     <row r="40" spans="1:19" ht="150" customHeight="1">
       <c r="B40" s="35"/>
       <c r="C40" s="520"/>
-      <c r="D40" s="266" t="s">
+      <c r="D40" s="265" t="s">
         <v>38</v>
       </c>
       <c r="E40" s="107" t="s">
@@ -11524,7 +11498,7 @@
     <row r="41" spans="1:19" ht="150" customHeight="1">
       <c r="B41" s="35"/>
       <c r="C41" s="520"/>
-      <c r="D41" s="266" t="s">
+      <c r="D41" s="265" t="s">
         <v>40</v>
       </c>
       <c r="E41" s="107" t="s">
@@ -11564,7 +11538,7 @@
     <row r="42" spans="1:19" ht="150" customHeight="1">
       <c r="B42" s="35"/>
       <c r="C42" s="520"/>
-      <c r="D42" s="266" t="s">
+      <c r="D42" s="265" t="s">
         <v>44</v>
       </c>
       <c r="E42" s="107" t="s">
@@ -11604,7 +11578,7 @@
     <row r="43" spans="1:19" ht="150" customHeight="1">
       <c r="B43" s="35"/>
       <c r="C43" s="520"/>
-      <c r="D43" s="266" t="s">
+      <c r="D43" s="265" t="s">
         <v>48</v>
       </c>
       <c r="E43" s="107" t="s">
@@ -11645,7 +11619,7 @@
       <c r="A44" s="14"/>
       <c r="B44" s="35"/>
       <c r="C44" s="520"/>
-      <c r="D44" s="267" t="s">
+      <c r="D44" s="266" t="s">
         <v>49</v>
       </c>
       <c r="E44" s="109" t="s">
@@ -11709,7 +11683,7 @@
       <c r="L46" s="42"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection sheet="1" selectLockedCells="1"/>
   <dataConsolidate link="1"/>
   <mergeCells count="22">
     <mergeCell ref="C2:K4"/>
@@ -11885,7 +11859,7 @@
     <col min="7" max="7" width="100.7109375" style="8" customWidth="1"/>
     <col min="8" max="9" width="120.7109375" style="8" customWidth="1"/>
     <col min="10" max="11" width="1.42578125" style="8" customWidth="1"/>
-    <col min="12" max="24" width="47.85546875" style="278"/>
+    <col min="12" max="24" width="47.85546875" style="277"/>
     <col min="25" max="16384" width="47.85546875" style="8"/>
   </cols>
   <sheetData>
@@ -11967,39 +11941,39 @@
     <row r="8" spans="2:24" s="23" customFormat="1" ht="50.1" customHeight="1" thickBot="1">
       <c r="B8" s="69"/>
       <c r="C8" s="61"/>
-      <c r="D8" s="272" t="s">
+      <c r="D8" s="271" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="273" t="s">
+      <c r="E8" s="272" t="s">
         <v>167</v>
       </c>
-      <c r="F8" s="273" t="s">
+      <c r="F8" s="272" t="s">
         <v>168</v>
       </c>
-      <c r="G8" s="273" t="s">
+      <c r="G8" s="272" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="273" t="s">
+      <c r="H8" s="272" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="274" t="s">
+      <c r="I8" s="273" t="s">
         <v>169</v>
       </c>
       <c r="J8" s="544"/>
       <c r="K8" s="68"/>
-      <c r="L8" s="279"/>
-      <c r="M8" s="279"/>
-      <c r="N8" s="279"/>
-      <c r="O8" s="279"/>
-      <c r="P8" s="279"/>
-      <c r="Q8" s="279"/>
-      <c r="R8" s="279"/>
-      <c r="S8" s="279"/>
-      <c r="T8" s="279"/>
-      <c r="U8" s="279"/>
-      <c r="V8" s="279"/>
-      <c r="W8" s="279"/>
-      <c r="X8" s="279"/>
+      <c r="L8" s="278"/>
+      <c r="M8" s="278"/>
+      <c r="N8" s="278"/>
+      <c r="O8" s="278"/>
+      <c r="P8" s="278"/>
+      <c r="Q8" s="278"/>
+      <c r="R8" s="278"/>
+      <c r="S8" s="278"/>
+      <c r="T8" s="278"/>
+      <c r="U8" s="278"/>
+      <c r="V8" s="278"/>
+      <c r="W8" s="278"/>
+      <c r="X8" s="278"/>
     </row>
     <row r="9" spans="2:24" ht="150" customHeight="1">
       <c r="B9" s="69"/>
@@ -12015,15 +11989,15 @@
         <f>IF(ISERROR(VLOOKUP(D9,'ALL QUESTIONS'!B1:G128,4,FALSE)),"",(VLOOKUP(D9,'ALL QUESTIONS'!B1:G128,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G9" s="277" t="str">
+      <c r="G9" s="276" t="str">
         <f>IF(ISERROR(VLOOKUP(D9,'ALL QUESTIONS'!B1:G128,3,FALSE)),"",(VLOOKUP(D9,'ALL QUESTIONS'!B1:G128,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H9" s="275" t="str">
+      <c r="H9" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D9,'ALL QUESTIONS'!B1:G128,5,FALSE)),"",(VLOOKUP(D9,'ALL QUESTIONS'!B1:G128,5,FALSE)))</f>
         <v/>
       </c>
-      <c r="I9" s="276" t="str">
+      <c r="I9" s="275" t="str">
         <f>IF(ISERROR(VLOOKUP(D9,'ALL QUESTIONS'!B1:G128,6,FALSE)),"",(VLOOKUP(D9,'ALL QUESTIONS'!B1:G128,6,FALSE)))</f>
         <v/>
       </c>
@@ -12044,11 +12018,11 @@
         <f>IF(ISERROR(VLOOKUP(D10,'ALL QUESTIONS'!B2:G129,4,FALSE)),"",(VLOOKUP(D10,'ALL QUESTIONS'!B2:G129,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G10" s="275" t="str">
+      <c r="G10" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D10,'ALL QUESTIONS'!B2:G129,3,FALSE)),"",(VLOOKUP(D10,'ALL QUESTIONS'!B2:G129,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H10" s="275" t="str">
+      <c r="H10" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D10,'ALL QUESTIONS'!B2:G129,5,FALSE)),"",(VLOOKUP(D10,'ALL QUESTIONS'!B2:G129,5,FALSE)))</f>
         <v/>
       </c>
@@ -12073,11 +12047,11 @@
         <f>IF(ISERROR(VLOOKUP(D11,'ALL QUESTIONS'!B3:G130,4,FALSE)),"",(VLOOKUP(D11,'ALL QUESTIONS'!B3:G130,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G11" s="275" t="str">
+      <c r="G11" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D11,'ALL QUESTIONS'!B3:G130,3,FALSE)),"",(VLOOKUP(D11,'ALL QUESTIONS'!B3:G130,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H11" s="275" t="str">
+      <c r="H11" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D11,'ALL QUESTIONS'!B3:G130,5,FALSE)),"",(VLOOKUP(D11,'ALL QUESTIONS'!B3:G130,5,FALSE)))</f>
         <v/>
       </c>
@@ -12102,11 +12076,11 @@
         <f>IF(ISERROR(VLOOKUP(D12,'ALL QUESTIONS'!B4:G131,4,FALSE)),"",(VLOOKUP(D12,'ALL QUESTIONS'!B4:G131,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G12" s="275" t="str">
+      <c r="G12" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D12,'ALL QUESTIONS'!B4:G131,3,FALSE)),"",(VLOOKUP(D12,'ALL QUESTIONS'!B4:G131,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H12" s="275" t="str">
+      <c r="H12" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D12,'ALL QUESTIONS'!B4:G131,5,FALSE)),"",(VLOOKUP(D12,'ALL QUESTIONS'!B4:G131,5,FALSE)))</f>
         <v/>
       </c>
@@ -12131,11 +12105,11 @@
         <f>IF(ISERROR(VLOOKUP(D13,'ALL QUESTIONS'!B5:G132,4,FALSE)),"",(VLOOKUP(D13,'ALL QUESTIONS'!B5:G132,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G13" s="275" t="str">
+      <c r="G13" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D13,'ALL QUESTIONS'!B5:G132,3,FALSE)),"",(VLOOKUP(D13,'ALL QUESTIONS'!B5:G132,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H13" s="275" t="str">
+      <c r="H13" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D13,'ALL QUESTIONS'!B5:G132,5,FALSE)),"",(VLOOKUP(D13,'ALL QUESTIONS'!B5:G132,5,FALSE)))</f>
         <v/>
       </c>
@@ -12160,11 +12134,11 @@
         <f>IF(ISERROR(VLOOKUP(D14,'ALL QUESTIONS'!B6:G133,4,FALSE)),"",(VLOOKUP(D14,'ALL QUESTIONS'!B6:G133,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G14" s="275" t="str">
+      <c r="G14" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D14,'ALL QUESTIONS'!B6:G133,3,FALSE)),"",(VLOOKUP(D14,'ALL QUESTIONS'!B6:G133,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H14" s="275" t="str">
+      <c r="H14" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D14,'ALL QUESTIONS'!B6:G133,5,FALSE)),"",(VLOOKUP(D14,'ALL QUESTIONS'!B6:G133,5,FALSE)))</f>
         <v/>
       </c>
@@ -12189,11 +12163,11 @@
         <f>IF(ISERROR(VLOOKUP(D15,'ALL QUESTIONS'!B7:G134,4,FALSE)),"",(VLOOKUP(D15,'ALL QUESTIONS'!B7:G134,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G15" s="275" t="str">
+      <c r="G15" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D15,'ALL QUESTIONS'!B7:G134,3,FALSE)),"",(VLOOKUP(D15,'ALL QUESTIONS'!B7:G134,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H15" s="275" t="str">
+      <c r="H15" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D15,'ALL QUESTIONS'!B7:G134,5,FALSE)),"",(VLOOKUP(D15,'ALL QUESTIONS'!B7:G134,5,FALSE)))</f>
         <v/>
       </c>
@@ -12218,11 +12192,11 @@
         <f>IF(ISERROR(VLOOKUP(D16,'ALL QUESTIONS'!B8:G135,4,FALSE)),"",(VLOOKUP(D16,'ALL QUESTIONS'!B8:G135,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G16" s="275" t="str">
+      <c r="G16" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D16,'ALL QUESTIONS'!B8:G135,3,FALSE)),"",(VLOOKUP(D16,'ALL QUESTIONS'!B8:G135,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H16" s="275" t="str">
+      <c r="H16" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D16,'ALL QUESTIONS'!B8:G135,5,FALSE)),"",(VLOOKUP(D16,'ALL QUESTIONS'!B8:G135,5,FALSE)))</f>
         <v/>
       </c>
@@ -12247,11 +12221,11 @@
         <f>IF(ISERROR(VLOOKUP(D17,'ALL QUESTIONS'!B9:G136,4,FALSE)),"",(VLOOKUP(D17,'ALL QUESTIONS'!B9:G136,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G17" s="275" t="str">
+      <c r="G17" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D17,'ALL QUESTIONS'!B9:G136,3,FALSE)),"",(VLOOKUP(D17,'ALL QUESTIONS'!B9:G136,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H17" s="275" t="str">
+      <c r="H17" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D17,'ALL QUESTIONS'!B9:G136,5,FALSE)),"",(VLOOKUP(D17,'ALL QUESTIONS'!B9:G136,5,FALSE)))</f>
         <v/>
       </c>
@@ -12276,11 +12250,11 @@
         <f>IF(ISERROR(VLOOKUP(D18,'ALL QUESTIONS'!B10:G137,4,FALSE)),"",(VLOOKUP(D18,'ALL QUESTIONS'!B10:G137,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G18" s="275" t="str">
+      <c r="G18" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D18,'ALL QUESTIONS'!B10:G137,3,FALSE)),"",(VLOOKUP(D18,'ALL QUESTIONS'!B10:G137,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H18" s="275" t="str">
+      <c r="H18" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D18,'ALL QUESTIONS'!B10:G137,5,FALSE)),"",(VLOOKUP(D18,'ALL QUESTIONS'!B10:G137,5,FALSE)))</f>
         <v/>
       </c>
@@ -12305,11 +12279,11 @@
         <f>IF(ISERROR(VLOOKUP(D19,'ALL QUESTIONS'!B11:G138,4,FALSE)),"",(VLOOKUP(D19,'ALL QUESTIONS'!B11:G138,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G19" s="275" t="str">
+      <c r="G19" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D19,'ALL QUESTIONS'!B11:G138,3,FALSE)),"",(VLOOKUP(D19,'ALL QUESTIONS'!B11:G138,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H19" s="275" t="str">
+      <c r="H19" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D19,'ALL QUESTIONS'!B11:G138,5,FALSE)),"",(VLOOKUP(D19,'ALL QUESTIONS'!B11:G138,5,FALSE)))</f>
         <v/>
       </c>
@@ -12334,11 +12308,11 @@
         <f>IF(ISERROR(VLOOKUP(D20,'ALL QUESTIONS'!B12:G139,4,FALSE)),"",(VLOOKUP(D20,'ALL QUESTIONS'!B12:G139,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G20" s="275" t="str">
+      <c r="G20" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D20,'ALL QUESTIONS'!B12:G139,3,FALSE)),"",(VLOOKUP(D20,'ALL QUESTIONS'!B12:G139,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H20" s="275" t="str">
+      <c r="H20" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D20,'ALL QUESTIONS'!B12:G139,5,FALSE)),"",(VLOOKUP(D20,'ALL QUESTIONS'!B12:G139,5,FALSE)))</f>
         <v/>
       </c>
@@ -12363,11 +12337,11 @@
         <f>IF(ISERROR(VLOOKUP(D21,'ALL QUESTIONS'!B13:G140,4,FALSE)),"",(VLOOKUP(D21,'ALL QUESTIONS'!B13:G140,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G21" s="275" t="str">
+      <c r="G21" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D21,'ALL QUESTIONS'!B13:G140,3,FALSE)),"",(VLOOKUP(D21,'ALL QUESTIONS'!B13:G140,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H21" s="275" t="str">
+      <c r="H21" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D21,'ALL QUESTIONS'!B13:G140,5,FALSE)),"",(VLOOKUP(D21,'ALL QUESTIONS'!B13:G140,5,FALSE)))</f>
         <v/>
       </c>
@@ -12392,11 +12366,11 @@
         <f>IF(ISERROR(VLOOKUP(D22,'ALL QUESTIONS'!B14:G141,4,FALSE)),"",(VLOOKUP(D22,'ALL QUESTIONS'!B14:G141,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G22" s="275" t="str">
+      <c r="G22" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D22,'ALL QUESTIONS'!B14:G141,3,FALSE)),"",(VLOOKUP(D22,'ALL QUESTIONS'!B14:G141,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H22" s="275" t="str">
+      <c r="H22" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D22,'ALL QUESTIONS'!B14:G141,5,FALSE)),"",(VLOOKUP(D22,'ALL QUESTIONS'!B14:G141,5,FALSE)))</f>
         <v/>
       </c>
@@ -12421,11 +12395,11 @@
         <f>IF(ISERROR(VLOOKUP(D23,'ALL QUESTIONS'!B15:G142,4,FALSE)),"",(VLOOKUP(D23,'ALL QUESTIONS'!B15:G142,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G23" s="275" t="str">
+      <c r="G23" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D23,'ALL QUESTIONS'!B15:G142,3,FALSE)),"",(VLOOKUP(D23,'ALL QUESTIONS'!B15:G142,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H23" s="275" t="str">
+      <c r="H23" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D23,'ALL QUESTIONS'!B15:G142,5,FALSE)),"",(VLOOKUP(D23,'ALL QUESTIONS'!B15:G142,5,FALSE)))</f>
         <v/>
       </c>
@@ -12450,11 +12424,11 @@
         <f>IF(ISERROR(VLOOKUP(D24,'ALL QUESTIONS'!B16:G143,4,FALSE)),"",(VLOOKUP(D24,'ALL QUESTIONS'!B16:G143,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G24" s="275" t="str">
+      <c r="G24" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D24,'ALL QUESTIONS'!B16:G143,3,FALSE)),"",(VLOOKUP(D24,'ALL QUESTIONS'!B16:G143,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H24" s="275" t="str">
+      <c r="H24" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D24,'ALL QUESTIONS'!B16:G143,5,FALSE)),"",(VLOOKUP(D24,'ALL QUESTIONS'!B16:G143,5,FALSE)))</f>
         <v/>
       </c>
@@ -12479,11 +12453,11 @@
         <f>IF(ISERROR(VLOOKUP(D25,'ALL QUESTIONS'!B17:G144,4,FALSE)),"",(VLOOKUP(D25,'ALL QUESTIONS'!B17:G144,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G25" s="275" t="str">
+      <c r="G25" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D25,'ALL QUESTIONS'!B17:G144,3,FALSE)),"",(VLOOKUP(D25,'ALL QUESTIONS'!B17:G144,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H25" s="275" t="str">
+      <c r="H25" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D25,'ALL QUESTIONS'!B17:G144,5,FALSE)),"",(VLOOKUP(D25,'ALL QUESTIONS'!B17:G144,5,FALSE)))</f>
         <v/>
       </c>
@@ -12508,11 +12482,11 @@
         <f>IF(ISERROR(VLOOKUP(D26,'ALL QUESTIONS'!B18:G145,4,FALSE)),"",(VLOOKUP(D26,'ALL QUESTIONS'!B18:G145,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G26" s="275" t="str">
+      <c r="G26" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D26,'ALL QUESTIONS'!B18:G145,3,FALSE)),"",(VLOOKUP(D26,'ALL QUESTIONS'!B18:G145,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H26" s="275" t="str">
+      <c r="H26" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D26,'ALL QUESTIONS'!B18:G145,5,FALSE)),"",(VLOOKUP(D26,'ALL QUESTIONS'!B18:G145,5,FALSE)))</f>
         <v/>
       </c>
@@ -12537,11 +12511,11 @@
         <f>IF(ISERROR(VLOOKUP(D27,'ALL QUESTIONS'!B19:G146,4,FALSE)),"",(VLOOKUP(D27,'ALL QUESTIONS'!B19:G146,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G27" s="275" t="str">
+      <c r="G27" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D27,'ALL QUESTIONS'!B19:G146,3,FALSE)),"",(VLOOKUP(D27,'ALL QUESTIONS'!B19:G146,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H27" s="275" t="str">
+      <c r="H27" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D27,'ALL QUESTIONS'!B19:G146,5,FALSE)),"",(VLOOKUP(D27,'ALL QUESTIONS'!B19:G146,5,FALSE)))</f>
         <v/>
       </c>
@@ -12566,11 +12540,11 @@
         <f>IF(ISERROR(VLOOKUP(D28,'ALL QUESTIONS'!B20:G147,4,FALSE)),"",(VLOOKUP(D28,'ALL QUESTIONS'!B20:G147,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G28" s="275" t="str">
+      <c r="G28" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D28,'ALL QUESTIONS'!B20:G147,3,FALSE)),"",(VLOOKUP(D28,'ALL QUESTIONS'!B20:G147,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H28" s="275" t="str">
+      <c r="H28" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D28,'ALL QUESTIONS'!B20:G147,5,FALSE)),"",(VLOOKUP(D28,'ALL QUESTIONS'!B20:G147,5,FALSE)))</f>
         <v/>
       </c>
@@ -12595,11 +12569,11 @@
         <f>IF(ISERROR(VLOOKUP(D29,'ALL QUESTIONS'!B21:G148,4,FALSE)),"",(VLOOKUP(D29,'ALL QUESTIONS'!B21:G148,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G29" s="275" t="str">
+      <c r="G29" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D29,'ALL QUESTIONS'!B21:G148,3,FALSE)),"",(VLOOKUP(D29,'ALL QUESTIONS'!B21:G148,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H29" s="275" t="str">
+      <c r="H29" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D29,'ALL QUESTIONS'!B21:G148,5,FALSE)),"",(VLOOKUP(D29,'ALL QUESTIONS'!B21:G148,5,FALSE)))</f>
         <v/>
       </c>
@@ -12624,11 +12598,11 @@
         <f>IF(ISERROR(VLOOKUP(D30,'ALL QUESTIONS'!B22:G149,4,FALSE)),"",(VLOOKUP(D30,'ALL QUESTIONS'!B22:G149,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G30" s="275" t="str">
+      <c r="G30" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D30,'ALL QUESTIONS'!B22:G149,3,FALSE)),"",(VLOOKUP(D30,'ALL QUESTIONS'!B22:G149,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H30" s="275" t="str">
+      <c r="H30" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D30,'ALL QUESTIONS'!B22:G149,5,FALSE)),"",(VLOOKUP(D30,'ALL QUESTIONS'!B22:G149,5,FALSE)))</f>
         <v/>
       </c>
@@ -12653,11 +12627,11 @@
         <f>IF(ISERROR(VLOOKUP(D31,'ALL QUESTIONS'!B23:G150,4,FALSE)),"",(VLOOKUP(D31,'ALL QUESTIONS'!B23:G150,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G31" s="275" t="str">
+      <c r="G31" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D31,'ALL QUESTIONS'!B23:G150,3,FALSE)),"",(VLOOKUP(D31,'ALL QUESTIONS'!B23:G150,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H31" s="275" t="str">
+      <c r="H31" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D31,'ALL QUESTIONS'!B23:G150,5,FALSE)),"",(VLOOKUP(D31,'ALL QUESTIONS'!B23:G150,5,FALSE)))</f>
         <v/>
       </c>
@@ -12682,11 +12656,11 @@
         <f>IF(ISERROR(VLOOKUP(D32,'ALL QUESTIONS'!B24:G151,4,FALSE)),"",(VLOOKUP(D32,'ALL QUESTIONS'!B24:G151,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G32" s="275" t="str">
+      <c r="G32" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D32,'ALL QUESTIONS'!B24:G151,3,FALSE)),"",(VLOOKUP(D32,'ALL QUESTIONS'!B24:G151,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H32" s="275" t="str">
+      <c r="H32" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D32,'ALL QUESTIONS'!B24:G151,5,FALSE)),"",(VLOOKUP(D32,'ALL QUESTIONS'!B24:G151,5,FALSE)))</f>
         <v/>
       </c>
@@ -12711,11 +12685,11 @@
         <f>IF(ISERROR(VLOOKUP(D33,'ALL QUESTIONS'!B25:G152,4,FALSE)),"",(VLOOKUP(D33,'ALL QUESTIONS'!B25:G152,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G33" s="275" t="str">
+      <c r="G33" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D33,'ALL QUESTIONS'!B25:G152,3,FALSE)),"",(VLOOKUP(D33,'ALL QUESTIONS'!B25:G152,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H33" s="275" t="str">
+      <c r="H33" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D33,'ALL QUESTIONS'!B25:G152,5,FALSE)),"",(VLOOKUP(D33,'ALL QUESTIONS'!B25:G152,5,FALSE)))</f>
         <v/>
       </c>
@@ -12740,11 +12714,11 @@
         <f>IF(ISERROR(VLOOKUP(D34,'ALL QUESTIONS'!B26:G153,4,FALSE)),"",(VLOOKUP(D34,'ALL QUESTIONS'!B26:G153,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G34" s="275" t="str">
+      <c r="G34" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D34,'ALL QUESTIONS'!B26:G153,3,FALSE)),"",(VLOOKUP(D34,'ALL QUESTIONS'!B26:G153,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H34" s="275" t="str">
+      <c r="H34" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D34,'ALL QUESTIONS'!B26:G153,5,FALSE)),"",(VLOOKUP(D34,'ALL QUESTIONS'!B26:G153,5,FALSE)))</f>
         <v/>
       </c>
@@ -12769,11 +12743,11 @@
         <f>IF(ISERROR(VLOOKUP(D35,'ALL QUESTIONS'!B27:G154,4,FALSE)),"",(VLOOKUP(D35,'ALL QUESTIONS'!B27:G154,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G35" s="275" t="str">
+      <c r="G35" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D35,'ALL QUESTIONS'!B27:G154,3,FALSE)),"",(VLOOKUP(D35,'ALL QUESTIONS'!B27:G154,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H35" s="275" t="str">
+      <c r="H35" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D35,'ALL QUESTIONS'!B27:G154,5,FALSE)),"",(VLOOKUP(D35,'ALL QUESTIONS'!B27:G154,5,FALSE)))</f>
         <v/>
       </c>
@@ -12798,11 +12772,11 @@
         <f>IF(ISERROR(VLOOKUP(D36,'ALL QUESTIONS'!B28:G155,4,FALSE)),"",(VLOOKUP(D36,'ALL QUESTIONS'!B28:G155,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G36" s="275" t="str">
+      <c r="G36" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D36,'ALL QUESTIONS'!B28:G155,3,FALSE)),"",(VLOOKUP(D36,'ALL QUESTIONS'!B28:G155,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H36" s="275" t="str">
+      <c r="H36" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D36,'ALL QUESTIONS'!B28:G155,5,FALSE)),"",(VLOOKUP(D36,'ALL QUESTIONS'!B28:G155,5,FALSE)))</f>
         <v/>
       </c>
@@ -12827,11 +12801,11 @@
         <f>IF(ISERROR(VLOOKUP(D37,'ALL QUESTIONS'!B29:G156,4,FALSE)),"",(VLOOKUP(D37,'ALL QUESTIONS'!B29:G156,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G37" s="275" t="str">
+      <c r="G37" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D37,'ALL QUESTIONS'!B29:G156,3,FALSE)),"",(VLOOKUP(D37,'ALL QUESTIONS'!B29:G156,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H37" s="275" t="str">
+      <c r="H37" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D37,'ALL QUESTIONS'!B29:G156,5,FALSE)),"",(VLOOKUP(D37,'ALL QUESTIONS'!B29:G156,5,FALSE)))</f>
         <v/>
       </c>
@@ -12856,11 +12830,11 @@
         <f>IF(ISERROR(VLOOKUP(D38,'ALL QUESTIONS'!B30:G157,4,FALSE)),"",(VLOOKUP(D38,'ALL QUESTIONS'!B30:G157,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G38" s="275" t="str">
+      <c r="G38" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D38,'ALL QUESTIONS'!B30:G157,3,FALSE)),"",(VLOOKUP(D38,'ALL QUESTIONS'!B30:G157,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H38" s="275" t="str">
+      <c r="H38" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D38,'ALL QUESTIONS'!B30:G157,5,FALSE)),"",(VLOOKUP(D38,'ALL QUESTIONS'!B30:G157,5,FALSE)))</f>
         <v/>
       </c>
@@ -12885,11 +12859,11 @@
         <f>IF(ISERROR(VLOOKUP(D39,'ALL QUESTIONS'!B31:G158,4,FALSE)),"",(VLOOKUP(D39,'ALL QUESTIONS'!B31:G158,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G39" s="275" t="str">
+      <c r="G39" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D39,'ALL QUESTIONS'!B31:G158,3,FALSE)),"",(VLOOKUP(D39,'ALL QUESTIONS'!B31:G158,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H39" s="275" t="str">
+      <c r="H39" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D39,'ALL QUESTIONS'!B31:G158,5,FALSE)),"",(VLOOKUP(D39,'ALL QUESTIONS'!B31:G158,5,FALSE)))</f>
         <v/>
       </c>
@@ -12914,11 +12888,11 @@
         <f>IF(ISERROR(VLOOKUP(D40,'ALL QUESTIONS'!B32:G159,4,FALSE)),"",(VLOOKUP(D40,'ALL QUESTIONS'!B32:G159,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G40" s="275" t="str">
+      <c r="G40" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D40,'ALL QUESTIONS'!B32:G159,3,FALSE)),"",(VLOOKUP(D40,'ALL QUESTIONS'!B32:G159,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H40" s="275" t="str">
+      <c r="H40" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D40,'ALL QUESTIONS'!B32:G159,5,FALSE)),"",(VLOOKUP(D40,'ALL QUESTIONS'!B32:G159,5,FALSE)))</f>
         <v/>
       </c>
@@ -12943,11 +12917,11 @@
         <f>IF(ISERROR(VLOOKUP(D41,'ALL QUESTIONS'!B33:G160,4,FALSE)),"",(VLOOKUP(D41,'ALL QUESTIONS'!B33:G160,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G41" s="275" t="str">
+      <c r="G41" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D41,'ALL QUESTIONS'!B33:G160,3,FALSE)),"",(VLOOKUP(D41,'ALL QUESTIONS'!B33:G160,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H41" s="275" t="str">
+      <c r="H41" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D41,'ALL QUESTIONS'!B33:G160,5,FALSE)),"",(VLOOKUP(D41,'ALL QUESTIONS'!B33:G160,5,FALSE)))</f>
         <v/>
       </c>
@@ -12972,11 +12946,11 @@
         <f>IF(ISERROR(VLOOKUP(D42,'ALL QUESTIONS'!B34:G161,4,FALSE)),"",(VLOOKUP(D42,'ALL QUESTIONS'!B34:G161,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G42" s="275" t="str">
+      <c r="G42" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D42,'ALL QUESTIONS'!B34:G161,3,FALSE)),"",(VLOOKUP(D42,'ALL QUESTIONS'!B34:G161,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H42" s="275" t="str">
+      <c r="H42" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D42,'ALL QUESTIONS'!B34:G161,5,FALSE)),"",(VLOOKUP(D42,'ALL QUESTIONS'!B34:G161,5,FALSE)))</f>
         <v/>
       </c>
@@ -13001,11 +12975,11 @@
         <f>IF(ISERROR(VLOOKUP(D43,'ALL QUESTIONS'!B35:G162,4,FALSE)),"",(VLOOKUP(D43,'ALL QUESTIONS'!B35:G162,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G43" s="275" t="str">
+      <c r="G43" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D43,'ALL QUESTIONS'!B35:G162,3,FALSE)),"",(VLOOKUP(D43,'ALL QUESTIONS'!B35:G162,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H43" s="275" t="str">
+      <c r="H43" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D43,'ALL QUESTIONS'!B35:G162,5,FALSE)),"",(VLOOKUP(D43,'ALL QUESTIONS'!B35:G162,5,FALSE)))</f>
         <v/>
       </c>
@@ -13030,11 +13004,11 @@
         <f>IF(ISERROR(VLOOKUP(D44,'ALL QUESTIONS'!B36:G163,4,FALSE)),"",(VLOOKUP(D44,'ALL QUESTIONS'!B36:G163,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G44" s="275" t="str">
+      <c r="G44" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D44,'ALL QUESTIONS'!B36:G163,3,FALSE)),"",(VLOOKUP(D44,'ALL QUESTIONS'!B36:G163,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H44" s="275" t="str">
+      <c r="H44" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D44,'ALL QUESTIONS'!B36:G163,5,FALSE)),"",(VLOOKUP(D44,'ALL QUESTIONS'!B36:G163,5,FALSE)))</f>
         <v/>
       </c>
@@ -13059,11 +13033,11 @@
         <f>IF(ISERROR(VLOOKUP(D45,'ALL QUESTIONS'!B37:G164,4,FALSE)),"",(VLOOKUP(D45,'ALL QUESTIONS'!B37:G164,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G45" s="275" t="str">
+      <c r="G45" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D45,'ALL QUESTIONS'!B37:G164,3,FALSE)),"",(VLOOKUP(D45,'ALL QUESTIONS'!B37:G164,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H45" s="275" t="str">
+      <c r="H45" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D45,'ALL QUESTIONS'!B37:G164,5,FALSE)),"",(VLOOKUP(D45,'ALL QUESTIONS'!B37:G164,5,FALSE)))</f>
         <v/>
       </c>
@@ -13088,11 +13062,11 @@
         <f>IF(ISERROR(VLOOKUP(D46,'ALL QUESTIONS'!B38:G165,4,FALSE)),"",(VLOOKUP(D46,'ALL QUESTIONS'!B38:G165,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G46" s="275" t="str">
+      <c r="G46" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D46,'ALL QUESTIONS'!B38:G165,3,FALSE)),"",(VLOOKUP(D46,'ALL QUESTIONS'!B38:G165,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H46" s="275" t="str">
+      <c r="H46" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D46,'ALL QUESTIONS'!B38:G165,5,FALSE)),"",(VLOOKUP(D46,'ALL QUESTIONS'!B38:G165,5,FALSE)))</f>
         <v/>
       </c>
@@ -13117,11 +13091,11 @@
         <f>IF(ISERROR(VLOOKUP(D47,'ALL QUESTIONS'!B39:G166,4,FALSE)),"",(VLOOKUP(D47,'ALL QUESTIONS'!B39:G166,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G47" s="275" t="str">
+      <c r="G47" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D47,'ALL QUESTIONS'!B39:G166,3,FALSE)),"",(VLOOKUP(D47,'ALL QUESTIONS'!B39:G166,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H47" s="275" t="str">
+      <c r="H47" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D47,'ALL QUESTIONS'!B39:G166,5,FALSE)),"",(VLOOKUP(D47,'ALL QUESTIONS'!B39:G166,5,FALSE)))</f>
         <v/>
       </c>
@@ -13146,11 +13120,11 @@
         <f>IF(ISERROR(VLOOKUP(D48,'ALL QUESTIONS'!B40:G167,4,FALSE)),"",(VLOOKUP(D48,'ALL QUESTIONS'!B40:G167,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G48" s="275" t="str">
+      <c r="G48" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D48,'ALL QUESTIONS'!B40:G167,3,FALSE)),"",(VLOOKUP(D48,'ALL QUESTIONS'!B40:G167,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H48" s="275" t="str">
+      <c r="H48" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D48,'ALL QUESTIONS'!B40:G167,5,FALSE)),"",(VLOOKUP(D48,'ALL QUESTIONS'!B40:G167,5,FALSE)))</f>
         <v/>
       </c>
@@ -13175,11 +13149,11 @@
         <f>IF(ISERROR(VLOOKUP(D49,'ALL QUESTIONS'!B41:G168,4,FALSE)),"",(VLOOKUP(D49,'ALL QUESTIONS'!B41:G168,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G49" s="275" t="str">
+      <c r="G49" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D49,'ALL QUESTIONS'!B41:G168,3,FALSE)),"",(VLOOKUP(D49,'ALL QUESTIONS'!B41:G168,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H49" s="275" t="str">
+      <c r="H49" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D49,'ALL QUESTIONS'!B41:G168,5,FALSE)),"",(VLOOKUP(D49,'ALL QUESTIONS'!B41:G168,5,FALSE)))</f>
         <v/>
       </c>
@@ -13204,11 +13178,11 @@
         <f>IF(ISERROR(VLOOKUP(D50,'ALL QUESTIONS'!B42:G169,4,FALSE)),"",(VLOOKUP(D50,'ALL QUESTIONS'!B42:G169,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G50" s="275" t="str">
+      <c r="G50" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D50,'ALL QUESTIONS'!B42:G169,3,FALSE)),"",(VLOOKUP(D50,'ALL QUESTIONS'!B42:G169,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H50" s="275" t="str">
+      <c r="H50" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D50,'ALL QUESTIONS'!B42:G169,5,FALSE)),"",(VLOOKUP(D50,'ALL QUESTIONS'!B42:G169,5,FALSE)))</f>
         <v/>
       </c>
@@ -13233,11 +13207,11 @@
         <f>IF(ISERROR(VLOOKUP(D51,'ALL QUESTIONS'!B43:G170,4,FALSE)),"",(VLOOKUP(D51,'ALL QUESTIONS'!B43:G170,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G51" s="275" t="str">
+      <c r="G51" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D51,'ALL QUESTIONS'!B43:G170,3,FALSE)),"",(VLOOKUP(D51,'ALL QUESTIONS'!B43:G170,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H51" s="275" t="str">
+      <c r="H51" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D51,'ALL QUESTIONS'!B43:G170,5,FALSE)),"",(VLOOKUP(D51,'ALL QUESTIONS'!B43:G170,5,FALSE)))</f>
         <v/>
       </c>
@@ -13262,11 +13236,11 @@
         <f>IF(ISERROR(VLOOKUP(D52,'ALL QUESTIONS'!B44:G171,4,FALSE)),"",(VLOOKUP(D52,'ALL QUESTIONS'!B44:G171,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G52" s="275" t="str">
+      <c r="G52" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D52,'ALL QUESTIONS'!B44:G171,3,FALSE)),"",(VLOOKUP(D52,'ALL QUESTIONS'!B44:G171,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H52" s="275" t="str">
+      <c r="H52" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D52,'ALL QUESTIONS'!B44:G171,5,FALSE)),"",(VLOOKUP(D52,'ALL QUESTIONS'!B44:G171,5,FALSE)))</f>
         <v/>
       </c>
@@ -13291,11 +13265,11 @@
         <f>IF(ISERROR(VLOOKUP(D53,'ALL QUESTIONS'!B45:G172,4,FALSE)),"",(VLOOKUP(D53,'ALL QUESTIONS'!B45:G172,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G53" s="275" t="str">
+      <c r="G53" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D53,'ALL QUESTIONS'!B45:G172,3,FALSE)),"",(VLOOKUP(D53,'ALL QUESTIONS'!B45:G172,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H53" s="275" t="str">
+      <c r="H53" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D53,'ALL QUESTIONS'!B45:G172,5,FALSE)),"",(VLOOKUP(D53,'ALL QUESTIONS'!B45:G172,5,FALSE)))</f>
         <v/>
       </c>
@@ -13320,11 +13294,11 @@
         <f>IF(ISERROR(VLOOKUP(D54,'ALL QUESTIONS'!B46:G173,4,FALSE)),"",(VLOOKUP(D54,'ALL QUESTIONS'!B46:G173,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G54" s="275" t="str">
+      <c r="G54" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D54,'ALL QUESTIONS'!B46:G173,3,FALSE)),"",(VLOOKUP(D54,'ALL QUESTIONS'!B46:G173,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H54" s="275" t="str">
+      <c r="H54" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D54,'ALL QUESTIONS'!B46:G173,5,FALSE)),"",(VLOOKUP(D54,'ALL QUESTIONS'!B46:G173,5,FALSE)))</f>
         <v/>
       </c>
@@ -13349,11 +13323,11 @@
         <f>IF(ISERROR(VLOOKUP(D55,'ALL QUESTIONS'!B47:G174,4,FALSE)),"",(VLOOKUP(D55,'ALL QUESTIONS'!B47:G174,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G55" s="275" t="str">
+      <c r="G55" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D55,'ALL QUESTIONS'!B47:G174,3,FALSE)),"",(VLOOKUP(D55,'ALL QUESTIONS'!B47:G174,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H55" s="275" t="str">
+      <c r="H55" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D55,'ALL QUESTIONS'!B47:G174,5,FALSE)),"",(VLOOKUP(D55,'ALL QUESTIONS'!B47:G174,5,FALSE)))</f>
         <v/>
       </c>
@@ -13378,11 +13352,11 @@
         <f>IF(ISERROR(VLOOKUP(D56,'ALL QUESTIONS'!B48:G175,4,FALSE)),"",(VLOOKUP(D56,'ALL QUESTIONS'!B48:G175,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G56" s="275" t="str">
+      <c r="G56" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D56,'ALL QUESTIONS'!B48:G175,3,FALSE)),"",(VLOOKUP(D56,'ALL QUESTIONS'!B48:G175,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H56" s="275" t="str">
+      <c r="H56" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D56,'ALL QUESTIONS'!B48:G175,5,FALSE)),"",(VLOOKUP(D56,'ALL QUESTIONS'!B48:G175,5,FALSE)))</f>
         <v/>
       </c>
@@ -13407,11 +13381,11 @@
         <f>IF(ISERROR(VLOOKUP(D57,'ALL QUESTIONS'!B49:G176,4,FALSE)),"",(VLOOKUP(D57,'ALL QUESTIONS'!B49:G176,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G57" s="275" t="str">
+      <c r="G57" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D57,'ALL QUESTIONS'!B49:G176,3,FALSE)),"",(VLOOKUP(D57,'ALL QUESTIONS'!B49:G176,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H57" s="275" t="str">
+      <c r="H57" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D57,'ALL QUESTIONS'!B49:G176,5,FALSE)),"",(VLOOKUP(D57,'ALL QUESTIONS'!B49:G176,5,FALSE)))</f>
         <v/>
       </c>
@@ -13436,11 +13410,11 @@
         <f>IF(ISERROR(VLOOKUP(D58,'ALL QUESTIONS'!B50:G177,4,FALSE)),"",(VLOOKUP(D58,'ALL QUESTIONS'!B50:G177,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G58" s="275" t="str">
+      <c r="G58" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D58,'ALL QUESTIONS'!B50:G177,3,FALSE)),"",(VLOOKUP(D58,'ALL QUESTIONS'!B50:G177,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H58" s="275" t="str">
+      <c r="H58" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D58,'ALL QUESTIONS'!B50:G177,5,FALSE)),"",(VLOOKUP(D58,'ALL QUESTIONS'!B50:G177,5,FALSE)))</f>
         <v/>
       </c>
@@ -13465,11 +13439,11 @@
         <f>IF(ISERROR(VLOOKUP(D59,'ALL QUESTIONS'!B51:G178,4,FALSE)),"",(VLOOKUP(D59,'ALL QUESTIONS'!B51:G178,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G59" s="275" t="str">
+      <c r="G59" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D59,'ALL QUESTIONS'!B51:G178,3,FALSE)),"",(VLOOKUP(D59,'ALL QUESTIONS'!B51:G178,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H59" s="275" t="str">
+      <c r="H59" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D59,'ALL QUESTIONS'!B51:G178,5,FALSE)),"",(VLOOKUP(D59,'ALL QUESTIONS'!B51:G178,5,FALSE)))</f>
         <v/>
       </c>
@@ -13494,11 +13468,11 @@
         <f>IF(ISERROR(VLOOKUP(D60,'ALL QUESTIONS'!B52:G179,4,FALSE)),"",(VLOOKUP(D60,'ALL QUESTIONS'!B52:G179,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G60" s="275" t="str">
+      <c r="G60" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D60,'ALL QUESTIONS'!B52:G179,3,FALSE)),"",(VLOOKUP(D60,'ALL QUESTIONS'!B52:G179,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H60" s="275" t="str">
+      <c r="H60" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D60,'ALL QUESTIONS'!B52:G179,5,FALSE)),"",(VLOOKUP(D60,'ALL QUESTIONS'!B52:G179,5,FALSE)))</f>
         <v/>
       </c>
@@ -13523,11 +13497,11 @@
         <f>IF(ISERROR(VLOOKUP(D61,'ALL QUESTIONS'!B53:G180,4,FALSE)),"",(VLOOKUP(D61,'ALL QUESTIONS'!B53:G180,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G61" s="275" t="str">
+      <c r="G61" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D61,'ALL QUESTIONS'!B53:G180,3,FALSE)),"",(VLOOKUP(D61,'ALL QUESTIONS'!B53:G180,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H61" s="275" t="str">
+      <c r="H61" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D61,'ALL QUESTIONS'!B53:G180,5,FALSE)),"",(VLOOKUP(D61,'ALL QUESTIONS'!B53:G180,5,FALSE)))</f>
         <v/>
       </c>
@@ -13552,11 +13526,11 @@
         <f>IF(ISERROR(VLOOKUP(D62,'ALL QUESTIONS'!B54:G181,4,FALSE)),"",(VLOOKUP(D62,'ALL QUESTIONS'!B54:G181,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G62" s="275" t="str">
+      <c r="G62" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D62,'ALL QUESTIONS'!B54:G181,3,FALSE)),"",(VLOOKUP(D62,'ALL QUESTIONS'!B54:G181,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H62" s="275" t="str">
+      <c r="H62" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D62,'ALL QUESTIONS'!B54:G181,5,FALSE)),"",(VLOOKUP(D62,'ALL QUESTIONS'!B54:G181,5,FALSE)))</f>
         <v/>
       </c>
@@ -13581,11 +13555,11 @@
         <f>IF(ISERROR(VLOOKUP(D63,'ALL QUESTIONS'!B55:G182,4,FALSE)),"",(VLOOKUP(D63,'ALL QUESTIONS'!B55:G182,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G63" s="275" t="str">
+      <c r="G63" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D63,'ALL QUESTIONS'!B55:G182,3,FALSE)),"",(VLOOKUP(D63,'ALL QUESTIONS'!B55:G182,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H63" s="275" t="str">
+      <c r="H63" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D63,'ALL QUESTIONS'!B55:G182,5,FALSE)),"",(VLOOKUP(D63,'ALL QUESTIONS'!B55:G182,5,FALSE)))</f>
         <v/>
       </c>
@@ -13610,11 +13584,11 @@
         <f>IF(ISERROR(VLOOKUP(D64,'ALL QUESTIONS'!B56:G183,4,FALSE)),"",(VLOOKUP(D64,'ALL QUESTIONS'!B56:G183,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G64" s="275" t="str">
+      <c r="G64" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D64,'ALL QUESTIONS'!B56:G183,3,FALSE)),"",(VLOOKUP(D64,'ALL QUESTIONS'!B56:G183,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H64" s="275" t="str">
+      <c r="H64" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D64,'ALL QUESTIONS'!B56:G183,5,FALSE)),"",(VLOOKUP(D64,'ALL QUESTIONS'!B56:G183,5,FALSE)))</f>
         <v/>
       </c>
@@ -13639,11 +13613,11 @@
         <f>IF(ISERROR(VLOOKUP(D65,'ALL QUESTIONS'!B57:G184,4,FALSE)),"",(VLOOKUP(D65,'ALL QUESTIONS'!B57:G184,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G65" s="275" t="str">
+      <c r="G65" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D65,'ALL QUESTIONS'!B57:G184,3,FALSE)),"",(VLOOKUP(D65,'ALL QUESTIONS'!B57:G184,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H65" s="275" t="str">
+      <c r="H65" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D65,'ALL QUESTIONS'!B57:G184,5,FALSE)),"",(VLOOKUP(D65,'ALL QUESTIONS'!B57:G184,5,FALSE)))</f>
         <v/>
       </c>
@@ -13668,11 +13642,11 @@
         <f>IF(ISERROR(VLOOKUP(D66,'ALL QUESTIONS'!B58:G185,4,FALSE)),"",(VLOOKUP(D66,'ALL QUESTIONS'!B58:G185,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G66" s="275" t="str">
+      <c r="G66" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D66,'ALL QUESTIONS'!B58:G185,3,FALSE)),"",(VLOOKUP(D66,'ALL QUESTIONS'!B58:G185,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H66" s="275" t="str">
+      <c r="H66" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D66,'ALL QUESTIONS'!B58:G185,5,FALSE)),"",(VLOOKUP(D66,'ALL QUESTIONS'!B58:G185,5,FALSE)))</f>
         <v/>
       </c>
@@ -13697,11 +13671,11 @@
         <f>IF(ISERROR(VLOOKUP(D67,'ALL QUESTIONS'!B59:G186,4,FALSE)),"",(VLOOKUP(D67,'ALL QUESTIONS'!B59:G186,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G67" s="275" t="str">
+      <c r="G67" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D67,'ALL QUESTIONS'!B59:G186,3,FALSE)),"",(VLOOKUP(D67,'ALL QUESTIONS'!B59:G186,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H67" s="275" t="str">
+      <c r="H67" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D67,'ALL QUESTIONS'!B59:G186,5,FALSE)),"",(VLOOKUP(D67,'ALL QUESTIONS'!B59:G186,5,FALSE)))</f>
         <v/>
       </c>
@@ -13726,11 +13700,11 @@
         <f>IF(ISERROR(VLOOKUP(D68,'ALL QUESTIONS'!B60:G187,4,FALSE)),"",(VLOOKUP(D68,'ALL QUESTIONS'!B60:G187,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G68" s="275" t="str">
+      <c r="G68" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D68,'ALL QUESTIONS'!B60:G187,3,FALSE)),"",(VLOOKUP(D68,'ALL QUESTIONS'!B60:G187,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H68" s="275" t="str">
+      <c r="H68" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D68,'ALL QUESTIONS'!B60:G187,5,FALSE)),"",(VLOOKUP(D68,'ALL QUESTIONS'!B60:G187,5,FALSE)))</f>
         <v/>
       </c>
@@ -13755,11 +13729,11 @@
         <f>IF(ISERROR(VLOOKUP(D69,'ALL QUESTIONS'!B61:G188,4,FALSE)),"",(VLOOKUP(D69,'ALL QUESTIONS'!B61:G188,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G69" s="275" t="str">
+      <c r="G69" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D69,'ALL QUESTIONS'!B61:G188,3,FALSE)),"",(VLOOKUP(D69,'ALL QUESTIONS'!B61:G188,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H69" s="275" t="str">
+      <c r="H69" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D69,'ALL QUESTIONS'!B61:G188,5,FALSE)),"",(VLOOKUP(D69,'ALL QUESTIONS'!B61:G188,5,FALSE)))</f>
         <v/>
       </c>
@@ -13784,11 +13758,11 @@
         <f>IF(ISERROR(VLOOKUP(D70,'ALL QUESTIONS'!B62:G189,4,FALSE)),"",(VLOOKUP(D70,'ALL QUESTIONS'!B62:G189,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G70" s="275" t="str">
+      <c r="G70" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D70,'ALL QUESTIONS'!B62:G189,3,FALSE)),"",(VLOOKUP(D70,'ALL QUESTIONS'!B62:G189,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H70" s="275" t="str">
+      <c r="H70" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D70,'ALL QUESTIONS'!B62:G189,5,FALSE)),"",(VLOOKUP(D70,'ALL QUESTIONS'!B62:G189,5,FALSE)))</f>
         <v/>
       </c>
@@ -13813,11 +13787,11 @@
         <f>IF(ISERROR(VLOOKUP(D71,'ALL QUESTIONS'!B63:G190,4,FALSE)),"",(VLOOKUP(D71,'ALL QUESTIONS'!B63:G190,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G71" s="275" t="str">
+      <c r="G71" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D71,'ALL QUESTIONS'!B63:G190,3,FALSE)),"",(VLOOKUP(D71,'ALL QUESTIONS'!B63:G190,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H71" s="275" t="str">
+      <c r="H71" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D71,'ALL QUESTIONS'!B63:G190,5,FALSE)),"",(VLOOKUP(D71,'ALL QUESTIONS'!B63:G190,5,FALSE)))</f>
         <v/>
       </c>
@@ -13842,11 +13816,11 @@
         <f>IF(ISERROR(VLOOKUP(D72,'ALL QUESTIONS'!B64:G191,4,FALSE)),"",(VLOOKUP(D72,'ALL QUESTIONS'!B64:G191,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G72" s="275" t="str">
+      <c r="G72" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D72,'ALL QUESTIONS'!B64:G191,3,FALSE)),"",(VLOOKUP(D72,'ALL QUESTIONS'!B64:G191,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H72" s="275" t="str">
+      <c r="H72" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D72,'ALL QUESTIONS'!B64:G191,5,FALSE)),"",(VLOOKUP(D72,'ALL QUESTIONS'!B64:G191,5,FALSE)))</f>
         <v/>
       </c>
@@ -13871,11 +13845,11 @@
         <f>IF(ISERROR(VLOOKUP(D73,'ALL QUESTIONS'!B65:G192,4,FALSE)),"",(VLOOKUP(D73,'ALL QUESTIONS'!B65:G192,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G73" s="275" t="str">
+      <c r="G73" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D73,'ALL QUESTIONS'!B65:G192,3,FALSE)),"",(VLOOKUP(D73,'ALL QUESTIONS'!B65:G192,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H73" s="275" t="str">
+      <c r="H73" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D73,'ALL QUESTIONS'!B65:G192,5,FALSE)),"",(VLOOKUP(D73,'ALL QUESTIONS'!B65:G192,5,FALSE)))</f>
         <v/>
       </c>
@@ -13900,11 +13874,11 @@
         <f>IF(ISERROR(VLOOKUP(D74,'ALL QUESTIONS'!B66:G193,4,FALSE)),"",(VLOOKUP(D74,'ALL QUESTIONS'!B66:G193,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G74" s="275" t="str">
+      <c r="G74" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D74,'ALL QUESTIONS'!B66:G193,3,FALSE)),"",(VLOOKUP(D74,'ALL QUESTIONS'!B66:G193,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H74" s="275" t="str">
+      <c r="H74" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D74,'ALL QUESTIONS'!B66:G193,5,FALSE)),"",(VLOOKUP(D74,'ALL QUESTIONS'!B66:G193,5,FALSE)))</f>
         <v/>
       </c>
@@ -13929,11 +13903,11 @@
         <f>IF(ISERROR(VLOOKUP(D75,'ALL QUESTIONS'!B67:G194,4,FALSE)),"",(VLOOKUP(D75,'ALL QUESTIONS'!B67:G194,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G75" s="275" t="str">
+      <c r="G75" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D75,'ALL QUESTIONS'!B67:G194,3,FALSE)),"",(VLOOKUP(D75,'ALL QUESTIONS'!B67:G194,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H75" s="275" t="str">
+      <c r="H75" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D75,'ALL QUESTIONS'!B67:G194,5,FALSE)),"",(VLOOKUP(D75,'ALL QUESTIONS'!B67:G194,5,FALSE)))</f>
         <v/>
       </c>
@@ -13958,11 +13932,11 @@
         <f>IF(ISERROR(VLOOKUP(D76,'ALL QUESTIONS'!B68:G195,4,FALSE)),"",(VLOOKUP(D76,'ALL QUESTIONS'!B68:G195,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G76" s="275" t="str">
+      <c r="G76" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D76,'ALL QUESTIONS'!B68:G195,3,FALSE)),"",(VLOOKUP(D76,'ALL QUESTIONS'!B68:G195,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H76" s="275" t="str">
+      <c r="H76" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D76,'ALL QUESTIONS'!B68:G195,5,FALSE)),"",(VLOOKUP(D76,'ALL QUESTIONS'!B68:G195,5,FALSE)))</f>
         <v/>
       </c>
@@ -13987,11 +13961,11 @@
         <f>IF(ISERROR(VLOOKUP(D77,'ALL QUESTIONS'!B69:G196,4,FALSE)),"",(VLOOKUP(D77,'ALL QUESTIONS'!B69:G196,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G77" s="275" t="str">
+      <c r="G77" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D77,'ALL QUESTIONS'!B69:G196,3,FALSE)),"",(VLOOKUP(D77,'ALL QUESTIONS'!B69:G196,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H77" s="275" t="str">
+      <c r="H77" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D77,'ALL QUESTIONS'!B69:G196,5,FALSE)),"",(VLOOKUP(D77,'ALL QUESTIONS'!B69:G196,5,FALSE)))</f>
         <v/>
       </c>
@@ -14016,11 +13990,11 @@
         <f>IF(ISERROR(VLOOKUP(D78,'ALL QUESTIONS'!B70:G197,4,FALSE)),"",(VLOOKUP(D78,'ALL QUESTIONS'!B70:G197,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G78" s="275" t="str">
+      <c r="G78" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D78,'ALL QUESTIONS'!B70:G197,3,FALSE)),"",(VLOOKUP(D78,'ALL QUESTIONS'!B70:G197,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H78" s="275" t="str">
+      <c r="H78" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D78,'ALL QUESTIONS'!B70:G197,5,FALSE)),"",(VLOOKUP(D78,'ALL QUESTIONS'!B70:G197,5,FALSE)))</f>
         <v/>
       </c>
@@ -14045,11 +14019,11 @@
         <f>IF(ISERROR(VLOOKUP(D79,'ALL QUESTIONS'!B71:G198,4,FALSE)),"",(VLOOKUP(D79,'ALL QUESTIONS'!B71:G198,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G79" s="275" t="str">
+      <c r="G79" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D79,'ALL QUESTIONS'!B71:G198,3,FALSE)),"",(VLOOKUP(D79,'ALL QUESTIONS'!B71:G198,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H79" s="275" t="str">
+      <c r="H79" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D79,'ALL QUESTIONS'!B71:G198,5,FALSE)),"",(VLOOKUP(D79,'ALL QUESTIONS'!B71:G198,5,FALSE)))</f>
         <v/>
       </c>
@@ -14074,11 +14048,11 @@
         <f>IF(ISERROR(VLOOKUP(D80,'ALL QUESTIONS'!B72:G199,4,FALSE)),"",(VLOOKUP(D80,'ALL QUESTIONS'!B72:G199,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G80" s="275" t="str">
+      <c r="G80" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D80,'ALL QUESTIONS'!B72:G199,3,FALSE)),"",(VLOOKUP(D80,'ALL QUESTIONS'!B72:G199,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H80" s="275" t="str">
+      <c r="H80" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D80,'ALL QUESTIONS'!B72:G199,5,FALSE)),"",(VLOOKUP(D80,'ALL QUESTIONS'!B72:G199,5,FALSE)))</f>
         <v/>
       </c>
@@ -14103,11 +14077,11 @@
         <f>IF(ISERROR(VLOOKUP(D81,'ALL QUESTIONS'!B73:G200,4,FALSE)),"",(VLOOKUP(D81,'ALL QUESTIONS'!B73:G200,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G81" s="275" t="str">
+      <c r="G81" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D81,'ALL QUESTIONS'!B73:G200,3,FALSE)),"",(VLOOKUP(D81,'ALL QUESTIONS'!B73:G200,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H81" s="275" t="str">
+      <c r="H81" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D81,'ALL QUESTIONS'!B73:G200,5,FALSE)),"",(VLOOKUP(D81,'ALL QUESTIONS'!B73:G200,5,FALSE)))</f>
         <v/>
       </c>
@@ -14132,11 +14106,11 @@
         <f>IF(ISERROR(VLOOKUP(D82,'ALL QUESTIONS'!B74:G201,4,FALSE)),"",(VLOOKUP(D82,'ALL QUESTIONS'!B74:G201,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G82" s="275" t="str">
+      <c r="G82" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D82,'ALL QUESTIONS'!B74:G201,3,FALSE)),"",(VLOOKUP(D82,'ALL QUESTIONS'!B74:G201,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H82" s="275" t="str">
+      <c r="H82" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D82,'ALL QUESTIONS'!B74:G201,5,FALSE)),"",(VLOOKUP(D82,'ALL QUESTIONS'!B74:G201,5,FALSE)))</f>
         <v/>
       </c>
@@ -14161,11 +14135,11 @@
         <f>IF(ISERROR(VLOOKUP(D83,'ALL QUESTIONS'!B75:G202,4,FALSE)),"",(VLOOKUP(D83,'ALL QUESTIONS'!B75:G202,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G83" s="275" t="str">
+      <c r="G83" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D83,'ALL QUESTIONS'!B75:G202,3,FALSE)),"",(VLOOKUP(D83,'ALL QUESTIONS'!B75:G202,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H83" s="275" t="str">
+      <c r="H83" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D83,'ALL QUESTIONS'!B75:G202,5,FALSE)),"",(VLOOKUP(D83,'ALL QUESTIONS'!B75:G202,5,FALSE)))</f>
         <v/>
       </c>
@@ -14190,11 +14164,11 @@
         <f>IF(ISERROR(VLOOKUP(D84,'ALL QUESTIONS'!B76:G203,4,FALSE)),"",(VLOOKUP(D84,'ALL QUESTIONS'!B76:G203,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G84" s="275" t="str">
+      <c r="G84" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D84,'ALL QUESTIONS'!B76:G203,3,FALSE)),"",(VLOOKUP(D84,'ALL QUESTIONS'!B76:G203,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H84" s="275" t="str">
+      <c r="H84" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D84,'ALL QUESTIONS'!B76:G203,5,FALSE)),"",(VLOOKUP(D84,'ALL QUESTIONS'!B76:G203,5,FALSE)))</f>
         <v/>
       </c>
@@ -14219,11 +14193,11 @@
         <f>IF(ISERROR(VLOOKUP(D85,'ALL QUESTIONS'!B77:G204,4,FALSE)),"",(VLOOKUP(D85,'ALL QUESTIONS'!B77:G204,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G85" s="275" t="str">
+      <c r="G85" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D85,'ALL QUESTIONS'!B77:G204,3,FALSE)),"",(VLOOKUP(D85,'ALL QUESTIONS'!B77:G204,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H85" s="275" t="str">
+      <c r="H85" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D85,'ALL QUESTIONS'!B77:G204,5,FALSE)),"",(VLOOKUP(D85,'ALL QUESTIONS'!B77:G204,5,FALSE)))</f>
         <v/>
       </c>
@@ -14248,11 +14222,11 @@
         <f>IF(ISERROR(VLOOKUP(D86,'ALL QUESTIONS'!B78:G205,4,FALSE)),"",(VLOOKUP(D86,'ALL QUESTIONS'!B78:G205,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G86" s="275" t="str">
+      <c r="G86" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D86,'ALL QUESTIONS'!B78:G205,3,FALSE)),"",(VLOOKUP(D86,'ALL QUESTIONS'!B78:G205,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H86" s="275" t="str">
+      <c r="H86" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D86,'ALL QUESTIONS'!B78:G205,5,FALSE)),"",(VLOOKUP(D86,'ALL QUESTIONS'!B78:G205,5,FALSE)))</f>
         <v/>
       </c>
@@ -14277,11 +14251,11 @@
         <f>IF(ISERROR(VLOOKUP(D87,'ALL QUESTIONS'!B79:G206,4,FALSE)),"",(VLOOKUP(D87,'ALL QUESTIONS'!B79:G206,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G87" s="275" t="str">
+      <c r="G87" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D87,'ALL QUESTIONS'!B79:G206,3,FALSE)),"",(VLOOKUP(D87,'ALL QUESTIONS'!B79:G206,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H87" s="275" t="str">
+      <c r="H87" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D87,'ALL QUESTIONS'!B79:G206,5,FALSE)),"",(VLOOKUP(D87,'ALL QUESTIONS'!B79:G206,5,FALSE)))</f>
         <v/>
       </c>
@@ -14306,11 +14280,11 @@
         <f>IF(ISERROR(VLOOKUP(D88,'ALL QUESTIONS'!B80:G207,4,FALSE)),"",(VLOOKUP(D88,'ALL QUESTIONS'!B80:G207,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G88" s="275" t="str">
+      <c r="G88" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D88,'ALL QUESTIONS'!B80:G207,3,FALSE)),"",(VLOOKUP(D88,'ALL QUESTIONS'!B80:G207,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H88" s="275" t="str">
+      <c r="H88" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D88,'ALL QUESTIONS'!B80:G207,5,FALSE)),"",(VLOOKUP(D88,'ALL QUESTIONS'!B80:G207,5,FALSE)))</f>
         <v/>
       </c>
@@ -14335,11 +14309,11 @@
         <f>IF(ISERROR(VLOOKUP(D89,'ALL QUESTIONS'!B81:G208,4,FALSE)),"",(VLOOKUP(D89,'ALL QUESTIONS'!B81:G208,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G89" s="275" t="str">
+      <c r="G89" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D89,'ALL QUESTIONS'!B81:G208,3,FALSE)),"",(VLOOKUP(D89,'ALL QUESTIONS'!B81:G208,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H89" s="275" t="str">
+      <c r="H89" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D89,'ALL QUESTIONS'!B81:G208,5,FALSE)),"",(VLOOKUP(D89,'ALL QUESTIONS'!B81:G208,5,FALSE)))</f>
         <v/>
       </c>
@@ -14364,11 +14338,11 @@
         <f>IF(ISERROR(VLOOKUP(D90,'ALL QUESTIONS'!B82:G209,4,FALSE)),"",(VLOOKUP(D90,'ALL QUESTIONS'!B82:G209,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G90" s="275" t="str">
+      <c r="G90" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D90,'ALL QUESTIONS'!B82:G209,3,FALSE)),"",(VLOOKUP(D90,'ALL QUESTIONS'!B82:G209,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H90" s="275" t="str">
+      <c r="H90" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D90,'ALL QUESTIONS'!B82:G209,5,FALSE)),"",(VLOOKUP(D90,'ALL QUESTIONS'!B82:G209,5,FALSE)))</f>
         <v/>
       </c>
@@ -14393,11 +14367,11 @@
         <f>IF(ISERROR(VLOOKUP(D91,'ALL QUESTIONS'!B83:G210,4,FALSE)),"",(VLOOKUP(D91,'ALL QUESTIONS'!B83:G210,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G91" s="275" t="str">
+      <c r="G91" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D91,'ALL QUESTIONS'!B83:G210,3,FALSE)),"",(VLOOKUP(D91,'ALL QUESTIONS'!B83:G210,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H91" s="275" t="str">
+      <c r="H91" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D91,'ALL QUESTIONS'!B83:G210,5,FALSE)),"",(VLOOKUP(D91,'ALL QUESTIONS'!B83:G210,5,FALSE)))</f>
         <v/>
       </c>
@@ -14422,11 +14396,11 @@
         <f>IF(ISERROR(VLOOKUP(D92,'ALL QUESTIONS'!B84:G211,4,FALSE)),"",(VLOOKUP(D92,'ALL QUESTIONS'!B84:G211,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G92" s="275" t="str">
+      <c r="G92" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D92,'ALL QUESTIONS'!B84:G211,3,FALSE)),"",(VLOOKUP(D92,'ALL QUESTIONS'!B84:G211,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H92" s="275" t="str">
+      <c r="H92" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D92,'ALL QUESTIONS'!B84:G211,5,FALSE)),"",(VLOOKUP(D92,'ALL QUESTIONS'!B84:G211,5,FALSE)))</f>
         <v/>
       </c>
@@ -14451,11 +14425,11 @@
         <f>IF(ISERROR(VLOOKUP(D93,'ALL QUESTIONS'!B85:G212,4,FALSE)),"",(VLOOKUP(D93,'ALL QUESTIONS'!B85:G212,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G93" s="275" t="str">
+      <c r="G93" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D93,'ALL QUESTIONS'!B85:G212,3,FALSE)),"",(VLOOKUP(D93,'ALL QUESTIONS'!B85:G212,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H93" s="275" t="str">
+      <c r="H93" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D93,'ALL QUESTIONS'!B85:G212,5,FALSE)),"",(VLOOKUP(D93,'ALL QUESTIONS'!B85:G212,5,FALSE)))</f>
         <v/>
       </c>
@@ -14480,11 +14454,11 @@
         <f>IF(ISERROR(VLOOKUP(D94,'ALL QUESTIONS'!B86:G213,4,FALSE)),"",(VLOOKUP(D94,'ALL QUESTIONS'!B86:G213,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G94" s="275" t="str">
+      <c r="G94" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D94,'ALL QUESTIONS'!B86:G213,3,FALSE)),"",(VLOOKUP(D94,'ALL QUESTIONS'!B86:G213,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H94" s="275" t="str">
+      <c r="H94" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D94,'ALL QUESTIONS'!B86:G213,5,FALSE)),"",(VLOOKUP(D94,'ALL QUESTIONS'!B86:G213,5,FALSE)))</f>
         <v/>
       </c>
@@ -14509,11 +14483,11 @@
         <f>IF(ISERROR(VLOOKUP(D95,'ALL QUESTIONS'!B87:G214,4,FALSE)),"",(VLOOKUP(D95,'ALL QUESTIONS'!B87:G214,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G95" s="275" t="str">
+      <c r="G95" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D95,'ALL QUESTIONS'!B87:G214,3,FALSE)),"",(VLOOKUP(D95,'ALL QUESTIONS'!B87:G214,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H95" s="275" t="str">
+      <c r="H95" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D95,'ALL QUESTIONS'!B87:G214,5,FALSE)),"",(VLOOKUP(D95,'ALL QUESTIONS'!B87:G214,5,FALSE)))</f>
         <v/>
       </c>
@@ -14538,11 +14512,11 @@
         <f>IF(ISERROR(VLOOKUP(D96,'ALL QUESTIONS'!B88:G215,4,FALSE)),"",(VLOOKUP(D96,'ALL QUESTIONS'!B88:G215,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G96" s="275" t="str">
+      <c r="G96" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D96,'ALL QUESTIONS'!B88:G215,3,FALSE)),"",(VLOOKUP(D96,'ALL QUESTIONS'!B88:G215,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H96" s="275" t="str">
+      <c r="H96" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D96,'ALL QUESTIONS'!B88:G215,5,FALSE)),"",(VLOOKUP(D96,'ALL QUESTIONS'!B88:G215,5,FALSE)))</f>
         <v/>
       </c>
@@ -14567,11 +14541,11 @@
         <f>IF(ISERROR(VLOOKUP(D97,'ALL QUESTIONS'!B89:G216,4,FALSE)),"",(VLOOKUP(D97,'ALL QUESTIONS'!B89:G216,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G97" s="275" t="str">
+      <c r="G97" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D97,'ALL QUESTIONS'!B89:G216,3,FALSE)),"",(VLOOKUP(D97,'ALL QUESTIONS'!B89:G216,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H97" s="275" t="str">
+      <c r="H97" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D97,'ALL QUESTIONS'!B89:G216,5,FALSE)),"",(VLOOKUP(D97,'ALL QUESTIONS'!B89:G216,5,FALSE)))</f>
         <v/>
       </c>
@@ -14596,11 +14570,11 @@
         <f>IF(ISERROR(VLOOKUP(D98,'ALL QUESTIONS'!B90:G217,4,FALSE)),"",(VLOOKUP(D98,'ALL QUESTIONS'!B90:G217,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G98" s="275" t="str">
+      <c r="G98" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D98,'ALL QUESTIONS'!B90:G217,3,FALSE)),"",(VLOOKUP(D98,'ALL QUESTIONS'!B90:G217,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H98" s="275" t="str">
+      <c r="H98" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D98,'ALL QUESTIONS'!B90:G217,5,FALSE)),"",(VLOOKUP(D98,'ALL QUESTIONS'!B90:G217,5,FALSE)))</f>
         <v/>
       </c>
@@ -14625,11 +14599,11 @@
         <f>IF(ISERROR(VLOOKUP(D99,'ALL QUESTIONS'!B91:G218,4,FALSE)),"",(VLOOKUP(D99,'ALL QUESTIONS'!B91:G218,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G99" s="275" t="str">
+      <c r="G99" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D99,'ALL QUESTIONS'!B91:G218,3,FALSE)),"",(VLOOKUP(D99,'ALL QUESTIONS'!B91:G218,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H99" s="275" t="str">
+      <c r="H99" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D99,'ALL QUESTIONS'!B91:G218,5,FALSE)),"",(VLOOKUP(D99,'ALL QUESTIONS'!B91:G218,5,FALSE)))</f>
         <v/>
       </c>
@@ -14654,11 +14628,11 @@
         <f>IF(ISERROR(VLOOKUP(D100,'ALL QUESTIONS'!B92:G219,4,FALSE)),"",(VLOOKUP(D100,'ALL QUESTIONS'!B92:G219,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G100" s="275" t="str">
+      <c r="G100" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D100,'ALL QUESTIONS'!B92:G219,3,FALSE)),"",(VLOOKUP(D100,'ALL QUESTIONS'!B92:G219,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H100" s="275" t="str">
+      <c r="H100" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D100,'ALL QUESTIONS'!B92:G219,5,FALSE)),"",(VLOOKUP(D100,'ALL QUESTIONS'!B92:G219,5,FALSE)))</f>
         <v/>
       </c>
@@ -14683,11 +14657,11 @@
         <f>IF(ISERROR(VLOOKUP(D101,'ALL QUESTIONS'!B93:G220,4,FALSE)),"",(VLOOKUP(D101,'ALL QUESTIONS'!B93:G220,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G101" s="275" t="str">
+      <c r="G101" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D101,'ALL QUESTIONS'!B93:G220,3,FALSE)),"",(VLOOKUP(D101,'ALL QUESTIONS'!B93:G220,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H101" s="275" t="str">
+      <c r="H101" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D101,'ALL QUESTIONS'!B93:G220,5,FALSE)),"",(VLOOKUP(D101,'ALL QUESTIONS'!B93:G220,5,FALSE)))</f>
         <v/>
       </c>
@@ -14712,11 +14686,11 @@
         <f>IF(ISERROR(VLOOKUP(D102,'ALL QUESTIONS'!B94:G221,4,FALSE)),"",(VLOOKUP(D102,'ALL QUESTIONS'!B94:G221,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G102" s="275" t="str">
+      <c r="G102" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D102,'ALL QUESTIONS'!B94:G221,3,FALSE)),"",(VLOOKUP(D102,'ALL QUESTIONS'!B94:G221,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H102" s="275" t="str">
+      <c r="H102" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D102,'ALL QUESTIONS'!B94:G221,5,FALSE)),"",(VLOOKUP(D102,'ALL QUESTIONS'!B94:G221,5,FALSE)))</f>
         <v/>
       </c>
@@ -14741,11 +14715,11 @@
         <f>IF(ISERROR(VLOOKUP(D103,'ALL QUESTIONS'!B95:G222,4,FALSE)),"",(VLOOKUP(D103,'ALL QUESTIONS'!B95:G222,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G103" s="275" t="str">
+      <c r="G103" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D103,'ALL QUESTIONS'!B95:G222,3,FALSE)),"",(VLOOKUP(D103,'ALL QUESTIONS'!B95:G222,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H103" s="275" t="str">
+      <c r="H103" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D103,'ALL QUESTIONS'!B95:G222,5,FALSE)),"",(VLOOKUP(D103,'ALL QUESTIONS'!B95:G222,5,FALSE)))</f>
         <v/>
       </c>
@@ -14770,11 +14744,11 @@
         <f>IF(ISERROR(VLOOKUP(D104,'ALL QUESTIONS'!B96:G223,4,FALSE)),"",(VLOOKUP(D104,'ALL QUESTIONS'!B96:G223,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G104" s="275" t="str">
+      <c r="G104" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D104,'ALL QUESTIONS'!B96:G223,3,FALSE)),"",(VLOOKUP(D104,'ALL QUESTIONS'!B96:G223,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H104" s="275" t="str">
+      <c r="H104" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D104,'ALL QUESTIONS'!B96:G223,5,FALSE)),"",(VLOOKUP(D104,'ALL QUESTIONS'!B96:G223,5,FALSE)))</f>
         <v/>
       </c>
@@ -14799,11 +14773,11 @@
         <f>IF(ISERROR(VLOOKUP(D105,'ALL QUESTIONS'!B97:G224,4,FALSE)),"",(VLOOKUP(D105,'ALL QUESTIONS'!B97:G224,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G105" s="275" t="str">
+      <c r="G105" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D105,'ALL QUESTIONS'!B97:G224,3,FALSE)),"",(VLOOKUP(D105,'ALL QUESTIONS'!B97:G224,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H105" s="275" t="str">
+      <c r="H105" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D105,'ALL QUESTIONS'!B97:G224,5,FALSE)),"",(VLOOKUP(D105,'ALL QUESTIONS'!B97:G224,5,FALSE)))</f>
         <v/>
       </c>
@@ -14828,11 +14802,11 @@
         <f>IF(ISERROR(VLOOKUP(D106,'ALL QUESTIONS'!B98:G225,4,FALSE)),"",(VLOOKUP(D106,'ALL QUESTIONS'!B98:G225,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G106" s="275" t="str">
+      <c r="G106" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D106,'ALL QUESTIONS'!B98:G225,3,FALSE)),"",(VLOOKUP(D106,'ALL QUESTIONS'!B98:G225,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H106" s="275" t="str">
+      <c r="H106" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D106,'ALL QUESTIONS'!B98:G225,5,FALSE)),"",(VLOOKUP(D106,'ALL QUESTIONS'!B98:G225,5,FALSE)))</f>
         <v/>
       </c>
@@ -14857,11 +14831,11 @@
         <f>IF(ISERROR(VLOOKUP(D107,'ALL QUESTIONS'!B99:G226,4,FALSE)),"",(VLOOKUP(D107,'ALL QUESTIONS'!B99:G226,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G107" s="275" t="str">
+      <c r="G107" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D107,'ALL QUESTIONS'!B99:G226,3,FALSE)),"",(VLOOKUP(D107,'ALL QUESTIONS'!B99:G226,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H107" s="275" t="str">
+      <c r="H107" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D107,'ALL QUESTIONS'!B99:G226,5,FALSE)),"",(VLOOKUP(D107,'ALL QUESTIONS'!B99:G226,5,FALSE)))</f>
         <v/>
       </c>
@@ -14886,11 +14860,11 @@
         <f>IF(ISERROR(VLOOKUP(D108,'ALL QUESTIONS'!B100:G227,4,FALSE)),"",(VLOOKUP(D108,'ALL QUESTIONS'!B100:G227,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G108" s="275" t="str">
+      <c r="G108" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D108,'ALL QUESTIONS'!B100:G227,3,FALSE)),"",(VLOOKUP(D108,'ALL QUESTIONS'!B100:G227,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H108" s="275" t="str">
+      <c r="H108" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D108,'ALL QUESTIONS'!B100:G227,5,FALSE)),"",(VLOOKUP(D108,'ALL QUESTIONS'!B100:G227,5,FALSE)))</f>
         <v/>
       </c>
@@ -14915,11 +14889,11 @@
         <f>IF(ISERROR(VLOOKUP(D109,'ALL QUESTIONS'!B101:G228,4,FALSE)),"",(VLOOKUP(D109,'ALL QUESTIONS'!B101:G228,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G109" s="275" t="str">
+      <c r="G109" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D109,'ALL QUESTIONS'!B101:G228,3,FALSE)),"",(VLOOKUP(D109,'ALL QUESTIONS'!B101:G228,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H109" s="275" t="str">
+      <c r="H109" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D109,'ALL QUESTIONS'!B101:G228,5,FALSE)),"",(VLOOKUP(D109,'ALL QUESTIONS'!B101:G228,5,FALSE)))</f>
         <v/>
       </c>
@@ -14944,11 +14918,11 @@
         <f>IF(ISERROR(VLOOKUP(D110,'ALL QUESTIONS'!B102:G229,4,FALSE)),"",(VLOOKUP(D110,'ALL QUESTIONS'!B102:G229,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G110" s="275" t="str">
+      <c r="G110" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D110,'ALL QUESTIONS'!B102:G229,3,FALSE)),"",(VLOOKUP(D110,'ALL QUESTIONS'!B102:G229,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H110" s="275" t="str">
+      <c r="H110" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D110,'ALL QUESTIONS'!B102:G229,5,FALSE)),"",(VLOOKUP(D110,'ALL QUESTIONS'!B102:G229,5,FALSE)))</f>
         <v/>
       </c>
@@ -14973,11 +14947,11 @@
         <f>IF(ISERROR(VLOOKUP(D111,'ALL QUESTIONS'!B103:G230,4,FALSE)),"",(VLOOKUP(D111,'ALL QUESTIONS'!B103:G230,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G111" s="275" t="str">
+      <c r="G111" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D111,'ALL QUESTIONS'!B103:G230,3,FALSE)),"",(VLOOKUP(D111,'ALL QUESTIONS'!B103:G230,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H111" s="275" t="str">
+      <c r="H111" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D111,'ALL QUESTIONS'!B103:G230,5,FALSE)),"",(VLOOKUP(D111,'ALL QUESTIONS'!B103:G230,5,FALSE)))</f>
         <v/>
       </c>
@@ -15002,11 +14976,11 @@
         <f>IF(ISERROR(VLOOKUP(D112,'ALL QUESTIONS'!B104:G231,4,FALSE)),"",(VLOOKUP(D112,'ALL QUESTIONS'!B104:G231,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G112" s="275" t="str">
+      <c r="G112" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D112,'ALL QUESTIONS'!B104:G231,3,FALSE)),"",(VLOOKUP(D112,'ALL QUESTIONS'!B104:G231,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H112" s="275" t="str">
+      <c r="H112" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D112,'ALL QUESTIONS'!B104:G231,5,FALSE)),"",(VLOOKUP(D112,'ALL QUESTIONS'!B104:G231,5,FALSE)))</f>
         <v/>
       </c>
@@ -15031,11 +15005,11 @@
         <f>IF(ISERROR(VLOOKUP(D113,'ALL QUESTIONS'!B105:G232,4,FALSE)),"",(VLOOKUP(D113,'ALL QUESTIONS'!B105:G232,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G113" s="275" t="str">
+      <c r="G113" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D113,'ALL QUESTIONS'!B105:G232,3,FALSE)),"",(VLOOKUP(D113,'ALL QUESTIONS'!B105:G232,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H113" s="275" t="str">
+      <c r="H113" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D113,'ALL QUESTIONS'!B105:G232,5,FALSE)),"",(VLOOKUP(D113,'ALL QUESTIONS'!B105:G232,5,FALSE)))</f>
         <v/>
       </c>
@@ -15060,11 +15034,11 @@
         <f>IF(ISERROR(VLOOKUP(D114,'ALL QUESTIONS'!B106:G233,4,FALSE)),"",(VLOOKUP(D114,'ALL QUESTIONS'!B106:G233,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G114" s="275" t="str">
+      <c r="G114" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D114,'ALL QUESTIONS'!B106:G233,3,FALSE)),"",(VLOOKUP(D114,'ALL QUESTIONS'!B106:G233,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H114" s="275" t="str">
+      <c r="H114" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D114,'ALL QUESTIONS'!B106:G233,5,FALSE)),"",(VLOOKUP(D114,'ALL QUESTIONS'!B106:G233,5,FALSE)))</f>
         <v/>
       </c>
@@ -15089,11 +15063,11 @@
         <f>IF(ISERROR(VLOOKUP(D115,'ALL QUESTIONS'!B107:G234,4,FALSE)),"",(VLOOKUP(D115,'ALL QUESTIONS'!B107:G234,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G115" s="275" t="str">
+      <c r="G115" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D115,'ALL QUESTIONS'!B107:G234,3,FALSE)),"",(VLOOKUP(D115,'ALL QUESTIONS'!B107:G234,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H115" s="275" t="str">
+      <c r="H115" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D115,'ALL QUESTIONS'!B107:G234,5,FALSE)),"",(VLOOKUP(D115,'ALL QUESTIONS'!B107:G234,5,FALSE)))</f>
         <v/>
       </c>
@@ -15118,11 +15092,11 @@
         <f>IF(ISERROR(VLOOKUP(D116,'ALL QUESTIONS'!B108:G235,4,FALSE)),"",(VLOOKUP(D116,'ALL QUESTIONS'!B108:G235,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G116" s="275" t="str">
+      <c r="G116" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D116,'ALL QUESTIONS'!B108:G235,3,FALSE)),"",(VLOOKUP(D116,'ALL QUESTIONS'!B108:G235,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H116" s="275" t="str">
+      <c r="H116" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D116,'ALL QUESTIONS'!B108:G235,5,FALSE)),"",(VLOOKUP(D116,'ALL QUESTIONS'!B108:G235,5,FALSE)))</f>
         <v/>
       </c>
@@ -15147,11 +15121,11 @@
         <f>IF(ISERROR(VLOOKUP(D117,'ALL QUESTIONS'!B109:G236,4,FALSE)),"",(VLOOKUP(D117,'ALL QUESTIONS'!B109:G236,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G117" s="275" t="str">
+      <c r="G117" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D117,'ALL QUESTIONS'!B109:G236,3,FALSE)),"",(VLOOKUP(D117,'ALL QUESTIONS'!B109:G236,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H117" s="275" t="str">
+      <c r="H117" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D117,'ALL QUESTIONS'!B109:G236,5,FALSE)),"",(VLOOKUP(D117,'ALL QUESTIONS'!B109:G236,5,FALSE)))</f>
         <v/>
       </c>
@@ -15176,11 +15150,11 @@
         <f>IF(ISERROR(VLOOKUP(D118,'ALL QUESTIONS'!B110:G237,4,FALSE)),"",(VLOOKUP(D118,'ALL QUESTIONS'!B110:G237,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G118" s="275" t="str">
+      <c r="G118" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D118,'ALL QUESTIONS'!B110:G237,3,FALSE)),"",(VLOOKUP(D118,'ALL QUESTIONS'!B110:G237,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H118" s="275" t="str">
+      <c r="H118" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D118,'ALL QUESTIONS'!B110:G237,5,FALSE)),"",(VLOOKUP(D118,'ALL QUESTIONS'!B110:G237,5,FALSE)))</f>
         <v/>
       </c>
@@ -15205,11 +15179,11 @@
         <f>IF(ISERROR(VLOOKUP(D119,'ALL QUESTIONS'!B111:G238,4,FALSE)),"",(VLOOKUP(D119,'ALL QUESTIONS'!B111:G238,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G119" s="275" t="str">
+      <c r="G119" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D119,'ALL QUESTIONS'!B111:G238,3,FALSE)),"",(VLOOKUP(D119,'ALL QUESTIONS'!B111:G238,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H119" s="275" t="str">
+      <c r="H119" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D119,'ALL QUESTIONS'!B111:G238,5,FALSE)),"",(VLOOKUP(D119,'ALL QUESTIONS'!B111:G238,5,FALSE)))</f>
         <v/>
       </c>
@@ -15234,11 +15208,11 @@
         <f>IF(ISERROR(VLOOKUP(D120,'ALL QUESTIONS'!B112:G239,4,FALSE)),"",(VLOOKUP(D120,'ALL QUESTIONS'!B112:G239,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G120" s="275" t="str">
+      <c r="G120" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D120,'ALL QUESTIONS'!B112:G239,3,FALSE)),"",(VLOOKUP(D120,'ALL QUESTIONS'!B112:G239,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H120" s="275" t="str">
+      <c r="H120" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D120,'ALL QUESTIONS'!B112:G239,5,FALSE)),"",(VLOOKUP(D120,'ALL QUESTIONS'!B112:G239,5,FALSE)))</f>
         <v/>
       </c>
@@ -15263,11 +15237,11 @@
         <f>IF(ISERROR(VLOOKUP(D121,'ALL QUESTIONS'!B113:G240,4,FALSE)),"",(VLOOKUP(D121,'ALL QUESTIONS'!B113:G240,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G121" s="275" t="str">
+      <c r="G121" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D121,'ALL QUESTIONS'!B113:G240,3,FALSE)),"",(VLOOKUP(D121,'ALL QUESTIONS'!B113:G240,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H121" s="275" t="str">
+      <c r="H121" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D121,'ALL QUESTIONS'!B113:G240,5,FALSE)),"",(VLOOKUP(D121,'ALL QUESTIONS'!B113:G240,5,FALSE)))</f>
         <v/>
       </c>
@@ -15292,11 +15266,11 @@
         <f>IF(ISERROR(VLOOKUP(D122,'ALL QUESTIONS'!B114:G241,4,FALSE)),"",(VLOOKUP(D122,'ALL QUESTIONS'!B114:G241,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G122" s="275" t="str">
+      <c r="G122" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D122,'ALL QUESTIONS'!B114:G241,3,FALSE)),"",(VLOOKUP(D122,'ALL QUESTIONS'!B114:G241,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H122" s="275" t="str">
+      <c r="H122" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D122,'ALL QUESTIONS'!B114:G241,5,FALSE)),"",(VLOOKUP(D122,'ALL QUESTIONS'!B114:G241,5,FALSE)))</f>
         <v/>
       </c>
@@ -15321,11 +15295,11 @@
         <f>IF(ISERROR(VLOOKUP(D123,'ALL QUESTIONS'!B115:G242,4,FALSE)),"",(VLOOKUP(D123,'ALL QUESTIONS'!B115:G242,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G123" s="275" t="str">
+      <c r="G123" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D123,'ALL QUESTIONS'!B115:G242,3,FALSE)),"",(VLOOKUP(D123,'ALL QUESTIONS'!B115:G242,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H123" s="275" t="str">
+      <c r="H123" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D123,'ALL QUESTIONS'!B115:G242,5,FALSE)),"",(VLOOKUP(D123,'ALL QUESTIONS'!B115:G242,5,FALSE)))</f>
         <v/>
       </c>
@@ -15350,11 +15324,11 @@
         <f>IF(ISERROR(VLOOKUP(D124,'ALL QUESTIONS'!B116:G243,4,FALSE)),"",(VLOOKUP(D124,'ALL QUESTIONS'!B116:G243,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G124" s="275" t="str">
+      <c r="G124" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D124,'ALL QUESTIONS'!B116:G243,3,FALSE)),"",(VLOOKUP(D124,'ALL QUESTIONS'!B116:G243,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H124" s="275" t="str">
+      <c r="H124" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D124,'ALL QUESTIONS'!B116:G243,5,FALSE)),"",(VLOOKUP(D124,'ALL QUESTIONS'!B116:G243,5,FALSE)))</f>
         <v/>
       </c>
@@ -15379,11 +15353,11 @@
         <f>IF(ISERROR(VLOOKUP(D125,'ALL QUESTIONS'!B117:G244,4,FALSE)),"",(VLOOKUP(D125,'ALL QUESTIONS'!B117:G244,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G125" s="275" t="str">
+      <c r="G125" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D125,'ALL QUESTIONS'!B117:G244,3,FALSE)),"",(VLOOKUP(D125,'ALL QUESTIONS'!B117:G244,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H125" s="275" t="str">
+      <c r="H125" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D125,'ALL QUESTIONS'!B117:G244,5,FALSE)),"",(VLOOKUP(D125,'ALL QUESTIONS'!B117:G244,5,FALSE)))</f>
         <v/>
       </c>
@@ -15408,11 +15382,11 @@
         <f>IF(ISERROR(VLOOKUP(D126,'ALL QUESTIONS'!B118:G245,4,FALSE)),"",(VLOOKUP(D126,'ALL QUESTIONS'!B118:G245,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G126" s="275" t="str">
+      <c r="G126" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D126,'ALL QUESTIONS'!B118:G245,3,FALSE)),"",(VLOOKUP(D126,'ALL QUESTIONS'!B118:G245,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H126" s="275" t="str">
+      <c r="H126" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D126,'ALL QUESTIONS'!B118:G245,5,FALSE)),"",(VLOOKUP(D126,'ALL QUESTIONS'!B118:G245,5,FALSE)))</f>
         <v/>
       </c>
@@ -15437,11 +15411,11 @@
         <f>IF(ISERROR(VLOOKUP(D127,'ALL QUESTIONS'!B119:G246,4,FALSE)),"",(VLOOKUP(D127,'ALL QUESTIONS'!B119:G246,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G127" s="275" t="str">
+      <c r="G127" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D127,'ALL QUESTIONS'!B119:G246,3,FALSE)),"",(VLOOKUP(D127,'ALL QUESTIONS'!B119:G246,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H127" s="275" t="str">
+      <c r="H127" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D127,'ALL QUESTIONS'!B119:G246,5,FALSE)),"",(VLOOKUP(D127,'ALL QUESTIONS'!B119:G246,5,FALSE)))</f>
         <v/>
       </c>
@@ -15466,11 +15440,11 @@
         <f>IF(ISERROR(VLOOKUP(D128,'ALL QUESTIONS'!B120:G247,4,FALSE)),"",(VLOOKUP(D128,'ALL QUESTIONS'!B120:G247,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G128" s="275" t="str">
+      <c r="G128" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D128,'ALL QUESTIONS'!B120:G247,3,FALSE)),"",(VLOOKUP(D128,'ALL QUESTIONS'!B120:G247,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H128" s="275" t="str">
+      <c r="H128" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D128,'ALL QUESTIONS'!B120:G247,5,FALSE)),"",(VLOOKUP(D128,'ALL QUESTIONS'!B120:G247,5,FALSE)))</f>
         <v/>
       </c>
@@ -15495,11 +15469,11 @@
         <f>IF(ISERROR(VLOOKUP(D129,'ALL QUESTIONS'!B121:G248,4,FALSE)),"",(VLOOKUP(D129,'ALL QUESTIONS'!B121:G248,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G129" s="275" t="str">
+      <c r="G129" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D129,'ALL QUESTIONS'!B121:G248,3,FALSE)),"",(VLOOKUP(D129,'ALL QUESTIONS'!B121:G248,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H129" s="275" t="str">
+      <c r="H129" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D129,'ALL QUESTIONS'!B121:G248,5,FALSE)),"",(VLOOKUP(D129,'ALL QUESTIONS'!B121:G248,5,FALSE)))</f>
         <v/>
       </c>
@@ -15524,11 +15498,11 @@
         <f>IF(ISERROR(VLOOKUP(D130,'ALL QUESTIONS'!B122:G249,4,FALSE)),"",(VLOOKUP(D130,'ALL QUESTIONS'!B122:G249,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G130" s="275" t="str">
+      <c r="G130" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D130,'ALL QUESTIONS'!B122:G249,3,FALSE)),"",(VLOOKUP(D130,'ALL QUESTIONS'!B122:G249,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H130" s="275" t="str">
+      <c r="H130" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D130,'ALL QUESTIONS'!B122:G249,5,FALSE)),"",(VLOOKUP(D130,'ALL QUESTIONS'!B122:G249,5,FALSE)))</f>
         <v/>
       </c>
@@ -15553,11 +15527,11 @@
         <f>IF(ISERROR(VLOOKUP(D131,'ALL QUESTIONS'!B123:G250,4,FALSE)),"",(VLOOKUP(D131,'ALL QUESTIONS'!B123:G250,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G131" s="275" t="str">
+      <c r="G131" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D131,'ALL QUESTIONS'!B123:G250,3,FALSE)),"",(VLOOKUP(D131,'ALL QUESTIONS'!B123:G250,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H131" s="275" t="str">
+      <c r="H131" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D131,'ALL QUESTIONS'!B123:G250,5,FALSE)),"",(VLOOKUP(D131,'ALL QUESTIONS'!B123:G250,5,FALSE)))</f>
         <v/>
       </c>
@@ -15582,11 +15556,11 @@
         <f>IF(ISERROR(VLOOKUP(D132,'ALL QUESTIONS'!B124:G251,4,FALSE)),"",(VLOOKUP(D132,'ALL QUESTIONS'!B124:G251,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G132" s="275" t="str">
+      <c r="G132" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D132,'ALL QUESTIONS'!B124:G251,3,FALSE)),"",(VLOOKUP(D132,'ALL QUESTIONS'!B124:G251,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H132" s="275" t="str">
+      <c r="H132" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D132,'ALL QUESTIONS'!B124:G251,5,FALSE)),"",(VLOOKUP(D132,'ALL QUESTIONS'!B124:G251,5,FALSE)))</f>
         <v/>
       </c>
@@ -15611,11 +15585,11 @@
         <f>IF(ISERROR(VLOOKUP(D133,'ALL QUESTIONS'!B125:G252,4,FALSE)),"",(VLOOKUP(D133,'ALL QUESTIONS'!B125:G252,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G133" s="275" t="str">
+      <c r="G133" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D133,'ALL QUESTIONS'!B125:G252,3,FALSE)),"",(VLOOKUP(D133,'ALL QUESTIONS'!B125:G252,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H133" s="275" t="str">
+      <c r="H133" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D133,'ALL QUESTIONS'!B125:G252,5,FALSE)),"",(VLOOKUP(D133,'ALL QUESTIONS'!B125:G252,5,FALSE)))</f>
         <v/>
       </c>
@@ -15640,11 +15614,11 @@
         <f>IF(ISERROR(VLOOKUP(D134,'ALL QUESTIONS'!B126:G253,4,FALSE)),"",(VLOOKUP(D134,'ALL QUESTIONS'!B126:G253,4,FALSE)))</f>
         <v/>
       </c>
-      <c r="G134" s="275" t="str">
+      <c r="G134" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D134,'ALL QUESTIONS'!B126:G253,3,FALSE)),"",(VLOOKUP(D134,'ALL QUESTIONS'!B126:G253,3,FALSE)))</f>
         <v/>
       </c>
-      <c r="H134" s="275" t="str">
+      <c r="H134" s="274" t="str">
         <f>IF(ISERROR(VLOOKUP(D134,'ALL QUESTIONS'!B126:G253,5,FALSE)),"",(VLOOKUP(D134,'ALL QUESTIONS'!B126:G253,5,FALSE)))</f>
         <v/>
       </c>
@@ -19513,6 +19487,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100262D0A0693E1774098A9D1B81A77D593" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8eef8b54c748df3ded63a75c66f8f161">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b798358c-1b41-4e04-a4da-b662e53c782f" xmlns:ns3="711594b2-0bb8-424b-a8a3-8cd428c60916" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5749473eb1a59a88148c1da22cc44c81" ns2:_="" ns3:_="">
     <xsd:import namespace="b798358c-1b41-4e04-a4da-b662e53c782f"/>
@@ -19689,22 +19672,21 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DC2C24E-FC0D-4D72-BA34-D8582685D6FD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9A8D52B-7001-485A-B139-D7BA38DA0863}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19723,19 +19705,11 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16CDE01D-4E58-4122-BC09-35D8F485F127}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DC2C24E-FC0D-4D72-BA34-D8582685D6FD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>